--- a/CS_100826/OMJ_CS_1408.xlsx
+++ b/CS_100826/OMJ_CS_1408.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pratik.SJFS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\latest\OPS-TOOL-V2\CS_100826\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18F27BB-C290-4C83-8DE5-7D5EBF724896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D22D43-4E40-4BC0-95CB-E74C77C78A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$R$1324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$D$1:$D$1325</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21323" uniqueCount="4326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20837" uniqueCount="4320">
   <si>
     <t>Client Style No</t>
   </si>
@@ -13932,24 +13932,9 @@
     <t>4.5</t>
   </si>
   <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
     <t>12.5</t>
   </si>
   <si>
-    <t>09</t>
-  </si>
-  <si>
     <t>7.5</t>
   </si>
   <si>
@@ -13957,9 +13942,6 @@
   </si>
   <si>
     <t>6.75</t>
-  </si>
-  <si>
-    <t>06</t>
   </si>
   <si>
     <t xml:space="preserve"> 3.75</t>
@@ -14392,6 +14374,9 @@
   </sheetPr>
   <dimension ref="A1:R1325"/>
   <sheetFormatPr defaultColWidth="18.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="137.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -14513,8 +14498,8 @@
       <c r="C3" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>4284</v>
+      <c r="D3" s="3">
+        <v>7</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>33</v>
@@ -14567,8 +14552,8 @@
       <c r="C4" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>4285</v>
+      <c r="D4" s="3">
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>40</v>
@@ -14675,8 +14660,8 @@
       <c r="C6" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>4286</v>
+      <c r="D6" s="3">
+        <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>57</v>
@@ -14729,8 +14714,8 @@
       <c r="C7" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>4287</v>
+      <c r="D7" s="3">
+        <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>64</v>
@@ -14784,7 +14769,7 @@
         <v>4274</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>4288</v>
+        <v>4284</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>71</v>
@@ -14837,8 +14822,8 @@
       <c r="C9" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4287</v>
+      <c r="D9" s="3">
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>64</v>
@@ -14891,8 +14876,8 @@
       <c r="C10" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4289</v>
+      <c r="D10" s="3">
+        <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>86</v>
@@ -14946,7 +14931,7 @@
         <v>4274</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>96</v>
@@ -15000,7 +14985,7 @@
         <v>4274</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>4291</v>
+        <v>4286</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>103</v>
@@ -15053,8 +15038,8 @@
       <c r="C13" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>4284</v>
+      <c r="D13" s="3">
+        <v>7</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>33</v>
@@ -15108,7 +15093,7 @@
         <v>4273</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>96</v>
@@ -15162,7 +15147,7 @@
         <v>4273</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>118</v>
@@ -15215,8 +15200,8 @@
       <c r="C16" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>4293</v>
+      <c r="D16" s="3">
+        <v>6</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>122</v>
@@ -15270,7 +15255,7 @@
         <v>4274</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>130</v>
@@ -15324,7 +15309,7 @@
         <v>4274</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>118</v>
@@ -15377,8 +15362,8 @@
       <c r="C19" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>4286</v>
+      <c r="D19" s="3">
+        <v>8</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>57</v>
@@ -15431,8 +15416,8 @@
       <c r="C20" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4284</v>
+      <c r="D20" s="3">
+        <v>7</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>33</v>
@@ -15485,8 +15470,8 @@
       <c r="C21" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4284</v>
+      <c r="D21" s="3">
+        <v>7</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>33</v>
@@ -15539,8 +15524,8 @@
       <c r="C22" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4284</v>
+      <c r="D22" s="3">
+        <v>7</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>33</v>
@@ -15594,7 +15579,7 @@
         <v>4273</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>96</v>
@@ -15700,7 +15685,7 @@
         <v>4273</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>177</v>
@@ -15808,7 +15793,7 @@
         <v>4273</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>4296</v>
+        <v>4290</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>188</v>
@@ -15861,8 +15846,8 @@
       <c r="C28" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>4284</v>
+      <c r="D28" s="3">
+        <v>7</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>33</v>
@@ -15915,8 +15900,8 @@
       <c r="C29" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>4284</v>
+      <c r="D29" s="3">
+        <v>7</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>33</v>
@@ -15969,8 +15954,8 @@
       <c r="C30" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>4284</v>
+      <c r="D30" s="3">
+        <v>7</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>33</v>
@@ -16021,8 +16006,8 @@
       <c r="C31" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>4284</v>
+      <c r="D31" s="3">
+        <v>7</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>33</v>
@@ -16072,7 +16057,7 @@
         <v>4274</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>215</v>
@@ -16126,7 +16111,7 @@
         <v>4273</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>222</v>
@@ -16180,7 +16165,7 @@
         <v>4274</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>227</v>
@@ -16234,7 +16219,7 @@
         <v>4273</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>130</v>
@@ -16288,7 +16273,7 @@
         <v>4273</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>96</v>
@@ -16342,7 +16327,7 @@
         <v>4274</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>242</v>
@@ -16396,7 +16381,7 @@
         <v>4273</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>215</v>
@@ -16450,7 +16435,7 @@
         <v>4274</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>252</v>
@@ -16503,8 +16488,8 @@
       <c r="C40" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>4287</v>
+      <c r="D40" s="3">
+        <v>5</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>64</v>
@@ -16558,7 +16543,7 @@
         <v>4274</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>263</v>
@@ -16612,7 +16597,7 @@
         <v>4273</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>268</v>
@@ -16720,7 +16705,7 @@
         <v>4274</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>227</v>
@@ -16821,8 +16806,8 @@
       <c r="C46" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>4289</v>
+      <c r="D46" s="3">
+        <v>9</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>86</v>
@@ -16876,7 +16861,7 @@
         <v>4274</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>293</v>
@@ -16929,8 +16914,8 @@
       <c r="C48" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4286</v>
+      <c r="D48" s="3">
+        <v>8</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>57</v>
@@ -16983,8 +16968,8 @@
       <c r="C49" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>4284</v>
+      <c r="D49" s="3">
+        <v>7</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>302</v>
@@ -17085,8 +17070,8 @@
       <c r="C51" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>4284</v>
+      <c r="D51" s="3">
+        <v>7</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>33</v>
@@ -17139,8 +17124,8 @@
       <c r="C52" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4284</v>
+      <c r="D52" s="3">
+        <v>7</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>33</v>
@@ -17194,7 +17179,7 @@
         <v>4276</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>326</v>
@@ -17248,7 +17233,7 @@
         <v>4273</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>333</v>
@@ -17301,8 +17286,8 @@
       <c r="C55" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>4284</v>
+      <c r="D55" s="3">
+        <v>7</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>33</v>
@@ -17355,8 +17340,8 @@
       <c r="C56" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>4284</v>
+      <c r="D56" s="3">
+        <v>7</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>33</v>
@@ -17409,8 +17394,8 @@
       <c r="C57" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4284</v>
+      <c r="D57" s="3">
+        <v>7</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>33</v>
@@ -17463,8 +17448,8 @@
       <c r="C58" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4284</v>
+      <c r="D58" s="3">
+        <v>7</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>33</v>
@@ -17517,8 +17502,8 @@
       <c r="C59" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4284</v>
+      <c r="D59" s="3">
+        <v>7</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>33</v>
@@ -17571,8 +17556,8 @@
       <c r="C60" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4284</v>
+      <c r="D60" s="3">
+        <v>7</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>33</v>
@@ -17625,8 +17610,8 @@
       <c r="C61" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>4286</v>
+      <c r="D61" s="3">
+        <v>8</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>57</v>
@@ -17679,8 +17664,8 @@
       <c r="C62" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4287</v>
+      <c r="D62" s="3">
+        <v>5</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>64</v>
@@ -17734,7 +17719,7 @@
         <v>4274</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>215</v>
@@ -17788,7 +17773,7 @@
         <v>4274</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>96</v>
@@ -17895,8 +17880,8 @@
       <c r="C66" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4285</v>
+      <c r="D66" s="3">
+        <v>4</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>40</v>
@@ -17949,8 +17934,8 @@
       <c r="C67" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>4284</v>
+      <c r="D67" s="3">
+        <v>7</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>33</v>
@@ -18004,7 +17989,7 @@
         <v>4274</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>222</v>
@@ -18058,7 +18043,7 @@
         <v>4274</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>130</v>
@@ -18165,8 +18150,8 @@
       <c r="C71" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>4293</v>
+      <c r="D71" s="3">
+        <v>6</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>122</v>
@@ -18219,8 +18204,8 @@
       <c r="C72" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4293</v>
+      <c r="D72" s="3">
+        <v>6</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>122</v>
@@ -18274,7 +18259,7 @@
         <v>4273</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>242</v>
@@ -18436,7 +18421,7 @@
         <v>4273</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>242</v>
@@ -18489,8 +18474,8 @@
       <c r="C77" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>4287</v>
+      <c r="D77" s="3">
+        <v>5</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>64</v>
@@ -18543,8 +18528,8 @@
       <c r="C78" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>4293</v>
+      <c r="D78" s="3">
+        <v>6</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>122</v>
@@ -18598,7 +18583,7 @@
         <v>4273</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>96</v>
@@ -18652,7 +18637,7 @@
         <v>4276</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>215</v>
@@ -18706,7 +18691,7 @@
         <v>4273</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>96</v>
@@ -18760,7 +18745,7 @@
         <v>4274</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>263</v>
@@ -18921,8 +18906,8 @@
       <c r="C85" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>4284</v>
+      <c r="D85" s="3">
+        <v>7</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>33</v>
@@ -18975,8 +18960,8 @@
       <c r="C86" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>4284</v>
+      <c r="D86" s="3">
+        <v>7</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>33</v>
@@ -19029,8 +19014,8 @@
       <c r="C87" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>4284</v>
+      <c r="D87" s="3">
+        <v>7</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>33</v>
@@ -19083,8 +19068,8 @@
       <c r="C88" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>4284</v>
+      <c r="D88" s="3">
+        <v>7</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>33</v>
@@ -19137,8 +19122,8 @@
       <c r="C89" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>4284</v>
+      <c r="D89" s="3">
+        <v>7</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>33</v>
@@ -19191,8 +19176,8 @@
       <c r="C90" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>4284</v>
+      <c r="D90" s="3">
+        <v>7</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>33</v>
@@ -19246,7 +19231,7 @@
         <v>4275</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>494</v>
@@ -19300,7 +19285,7 @@
         <v>4273</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>498</v>
@@ -19354,7 +19339,7 @@
         <v>4273</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>326</v>
@@ -19408,7 +19393,7 @@
         <v>4273</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>215</v>
@@ -19461,8 +19446,8 @@
       <c r="C95" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>4284</v>
+      <c r="D95" s="3">
+        <v>7</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>33</v>
@@ -19515,8 +19500,8 @@
       <c r="C96" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4284</v>
+      <c r="D96" s="3">
+        <v>7</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>33</v>
@@ -19569,8 +19554,8 @@
       <c r="C97" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>4284</v>
+      <c r="D97" s="3">
+        <v>7</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>33</v>
@@ -19623,8 +19608,8 @@
       <c r="C98" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>4284</v>
+      <c r="D98" s="3">
+        <v>7</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>33</v>
@@ -19677,8 +19662,8 @@
       <c r="C99" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>4284</v>
+      <c r="D99" s="3">
+        <v>7</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>33</v>
@@ -19731,8 +19716,8 @@
       <c r="C100" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4284</v>
+      <c r="D100" s="3">
+        <v>7</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>33</v>
@@ -19785,8 +19770,8 @@
       <c r="C101" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4284</v>
+      <c r="D101" s="3">
+        <v>7</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>33</v>
@@ -19839,8 +19824,8 @@
       <c r="C102" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>4284</v>
+      <c r="D102" s="3">
+        <v>7</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>33</v>
@@ -19893,8 +19878,8 @@
       <c r="C103" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>4284</v>
+      <c r="D103" s="3">
+        <v>7</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>33</v>
@@ -19947,8 +19932,8 @@
       <c r="C104" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>4284</v>
+      <c r="D104" s="3">
+        <v>7</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>33</v>
@@ -20001,8 +19986,8 @@
       <c r="C105" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>4289</v>
+      <c r="D105" s="3">
+        <v>9</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>86</v>
@@ -20056,7 +20041,7 @@
         <v>4274</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>4307</v>
+        <v>4301</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>556</v>
@@ -20110,7 +20095,7 @@
         <v>4274</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>498</v>
@@ -20163,8 +20148,8 @@
       <c r="C108" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>4293</v>
+      <c r="D108" s="3">
+        <v>6</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>122</v>
@@ -20218,7 +20203,7 @@
         <v>4275</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>566</v>
@@ -20272,7 +20257,7 @@
         <v>4274</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>227</v>
@@ -20326,7 +20311,7 @@
         <v>4275</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>242</v>
@@ -20380,7 +20365,7 @@
         <v>4274</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>4309</v>
+        <v>4303</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>580</v>
@@ -20434,7 +20419,7 @@
         <v>4274</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>263</v>
@@ -20596,7 +20581,7 @@
         <v>4274</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>242</v>
@@ -20649,8 +20634,8 @@
       <c r="C117" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>4293</v>
+      <c r="D117" s="3">
+        <v>6</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>122</v>
@@ -20703,8 +20688,8 @@
       <c r="C118" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>4287</v>
+      <c r="D118" s="3">
+        <v>5</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>64</v>
@@ -20757,8 +20742,8 @@
       <c r="C119" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D119" s="3" t="s">
-        <v>4286</v>
+      <c r="D119" s="3">
+        <v>8</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>57</v>
@@ -20812,7 +20797,7 @@
         <v>4274</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>498</v>
@@ -20866,7 +20851,7 @@
         <v>4275</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>4310</v>
+        <v>4304</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>613</v>
@@ -20919,8 +20904,8 @@
       <c r="C122" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>4284</v>
+      <c r="D122" s="3">
+        <v>7</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>33</v>
@@ -20974,7 +20959,7 @@
         <v>4273</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>215</v>
@@ -21082,7 +21067,7 @@
         <v>4274</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>96</v>
@@ -21136,7 +21121,7 @@
         <v>4273</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>227</v>
@@ -21189,8 +21174,8 @@
       <c r="C127" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>4284</v>
+      <c r="D127" s="3">
+        <v>7</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>33</v>
@@ -21244,7 +21229,7 @@
         <v>4273</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>215</v>
@@ -21298,7 +21283,7 @@
         <v>4275</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>498</v>
@@ -21352,7 +21337,7 @@
         <v>4273</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>227</v>
@@ -21455,8 +21440,8 @@
       <c r="C132" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D132" s="3" t="s">
-        <v>4293</v>
+      <c r="D132" s="3">
+        <v>6</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>122</v>
@@ -21510,7 +21495,7 @@
         <v>4273</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>4309</v>
+        <v>4303</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>580</v>
@@ -21563,8 +21548,8 @@
       <c r="C134" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D134" s="3" t="s">
-        <v>4286</v>
+      <c r="D134" s="3">
+        <v>8</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>57</v>
@@ -21617,8 +21602,8 @@
       <c r="C135" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>4293</v>
+      <c r="D135" s="3">
+        <v>6</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>122</v>
@@ -21722,7 +21707,7 @@
         <v>4274</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>215</v>
@@ -21776,7 +21761,7 @@
         <v>4274</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>215</v>
@@ -21827,8 +21812,8 @@
       <c r="C139" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D139" s="3" t="s">
-        <v>4293</v>
+      <c r="D139" s="3">
+        <v>6</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>122</v>
@@ -21932,7 +21917,7 @@
         <v>4274</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>4311</v>
+        <v>4305</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>689</v>
@@ -21985,8 +21970,8 @@
       <c r="C142" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D142" s="3" t="s">
-        <v>4293</v>
+      <c r="D142" s="3">
+        <v>6</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>122</v>
@@ -22040,7 +22025,7 @@
         <v>4273</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>215</v>
@@ -22094,7 +22079,7 @@
         <v>4274</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>215</v>
@@ -22148,7 +22133,7 @@
         <v>4274</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>566</v>
@@ -22201,8 +22186,8 @@
       <c r="C146" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D146" s="3" t="s">
-        <v>4284</v>
+      <c r="D146" s="3">
+        <v>7</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>33</v>
@@ -22255,8 +22240,8 @@
       <c r="C147" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D147" s="3" t="s">
-        <v>4284</v>
+      <c r="D147" s="3">
+        <v>7</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>33</v>
@@ -22309,8 +22294,8 @@
       <c r="C148" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D148" s="3" t="s">
-        <v>4284</v>
+      <c r="D148" s="3">
+        <v>7</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>33</v>
@@ -22364,7 +22349,7 @@
         <v>4274</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>4296</v>
+        <v>4290</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>188</v>
@@ -22417,8 +22402,8 @@
       <c r="C150" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D150" s="3" t="s">
-        <v>4289</v>
+      <c r="D150" s="3">
+        <v>9</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>86</v>
@@ -22472,7 +22457,7 @@
         <v>4274</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>215</v>
@@ -22525,8 +22510,8 @@
       <c r="C152" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D152" s="3" t="s">
-        <v>4293</v>
+      <c r="D152" s="3">
+        <v>6</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>122</v>
@@ -22580,7 +22565,7 @@
         <v>4273</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>498</v>
@@ -22633,8 +22618,8 @@
       <c r="C154" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D154" s="3" t="s">
-        <v>4293</v>
+      <c r="D154" s="3">
+        <v>6</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>122</v>
@@ -22688,7 +22673,7 @@
         <v>4274</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>215</v>
@@ -22741,8 +22726,8 @@
       <c r="C156" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D156" s="3" t="s">
-        <v>4293</v>
+      <c r="D156" s="3">
+        <v>6</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>122</v>
@@ -22796,7 +22781,7 @@
         <v>4274</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>4312</v>
+        <v>4306</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>749</v>
@@ -22849,8 +22834,8 @@
       <c r="C158" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D158" s="3" t="s">
-        <v>4293</v>
+      <c r="D158" s="3">
+        <v>6</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>122</v>
@@ -22904,7 +22889,7 @@
         <v>4274</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>215</v>
@@ -22957,8 +22942,8 @@
       <c r="C160" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D160" s="3" t="s">
-        <v>4293</v>
+      <c r="D160" s="3">
+        <v>6</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>122</v>
@@ -23011,8 +22996,8 @@
       <c r="C161" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D161" s="3" t="s">
-        <v>4286</v>
+      <c r="D161" s="3">
+        <v>8</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>57</v>
@@ -23066,7 +23051,7 @@
         <v>4274</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>566</v>
@@ -23120,7 +23105,7 @@
         <v>4273</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>333</v>
@@ -23174,7 +23159,7 @@
         <v>4274</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>215</v>
@@ -23228,7 +23213,7 @@
         <v>4273</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>498</v>
@@ -23281,8 +23266,8 @@
       <c r="C166" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D166" s="3" t="s">
-        <v>4293</v>
+      <c r="D166" s="3">
+        <v>6</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>122</v>
@@ -23336,7 +23321,7 @@
         <v>4273</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>215</v>
@@ -23444,7 +23429,7 @@
         <v>4273</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>498</v>
@@ -23639,8 +23624,8 @@
       <c r="C173" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D173" s="3" t="s">
-        <v>4284</v>
+      <c r="D173" s="3">
+        <v>7</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>33</v>
@@ -23693,8 +23678,8 @@
       <c r="C174" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D174" s="3" t="s">
-        <v>4285</v>
+      <c r="D174" s="3">
+        <v>4</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>40</v>
@@ -23747,8 +23732,8 @@
       <c r="C175" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D175" s="3" t="s">
-        <v>4284</v>
+      <c r="D175" s="3">
+        <v>7</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>33</v>
@@ -23802,7 +23787,7 @@
         <v>4275</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>498</v>
@@ -23856,7 +23841,7 @@
         <v>4274</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>215</v>
@@ -23905,8 +23890,8 @@
       <c r="C178" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D178" s="3" t="s">
-        <v>4284</v>
+      <c r="D178" s="3">
+        <v>7</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>33</v>
@@ -23960,7 +23945,7 @@
         <v>4273</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>263</v>
@@ -24014,7 +23999,7 @@
         <v>4274</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>263</v>
@@ -24067,8 +24052,8 @@
       <c r="C181" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D181" s="3" t="s">
-        <v>4284</v>
+      <c r="D181" s="3">
+        <v>7</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>33</v>
@@ -24170,7 +24155,7 @@
         <v>4273</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>4313</v>
+        <v>4307</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>844</v>
@@ -24219,8 +24204,8 @@
       <c r="C184" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D184" s="3" t="s">
-        <v>4284</v>
+      <c r="D184" s="3">
+        <v>7</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>33</v>
@@ -24273,8 +24258,8 @@
       <c r="C185" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D185" s="3" t="s">
-        <v>4284</v>
+      <c r="D185" s="3">
+        <v>7</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>33</v>
@@ -24327,8 +24312,8 @@
       <c r="C186" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D186" s="3" t="s">
-        <v>4284</v>
+      <c r="D186" s="3">
+        <v>7</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>33</v>
@@ -24381,8 +24366,8 @@
       <c r="C187" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D187" s="3" t="s">
-        <v>4284</v>
+      <c r="D187" s="3">
+        <v>7</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>33</v>
@@ -24435,8 +24420,8 @@
       <c r="C188" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D188" s="3" t="s">
-        <v>4284</v>
+      <c r="D188" s="3">
+        <v>7</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>33</v>
@@ -24489,8 +24474,8 @@
       <c r="C189" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D189" s="3" t="s">
-        <v>4284</v>
+      <c r="D189" s="3">
+        <v>7</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>33</v>
@@ -24543,8 +24528,8 @@
       <c r="C190" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D190" s="3" t="s">
-        <v>4284</v>
+      <c r="D190" s="3">
+        <v>7</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>33</v>
@@ -24597,8 +24582,8 @@
       <c r="C191" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D191" s="3" t="s">
-        <v>4284</v>
+      <c r="D191" s="3">
+        <v>7</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>33</v>
@@ -24652,7 +24637,7 @@
         <v>4274</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>252</v>
@@ -24705,8 +24690,8 @@
       <c r="C193" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D193" s="3" t="s">
-        <v>4286</v>
+      <c r="D193" s="3">
+        <v>8</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>57</v>
@@ -24760,7 +24745,7 @@
         <v>4273</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>215</v>
@@ -24813,8 +24798,8 @@
       <c r="C195" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D195" s="3" t="s">
-        <v>4293</v>
+      <c r="D195" s="3">
+        <v>6</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>122</v>
@@ -24867,8 +24852,8 @@
       <c r="C196" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D196" s="3" t="s">
-        <v>4286</v>
+      <c r="D196" s="3">
+        <v>8</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>57</v>
@@ -24921,8 +24906,8 @@
       <c r="C197" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D197" s="3" t="s">
-        <v>4293</v>
+      <c r="D197" s="3">
+        <v>6</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>896</v>
@@ -24975,8 +24960,8 @@
       <c r="C198" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D198" s="3" t="s">
-        <v>4293</v>
+      <c r="D198" s="3">
+        <v>6</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>122</v>
@@ -25025,8 +25010,8 @@
       <c r="C199" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D199" s="3" t="s">
-        <v>4293</v>
+      <c r="D199" s="3">
+        <v>6</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>896</v>
@@ -25079,8 +25064,8 @@
       <c r="C200" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D200" s="3" t="s">
-        <v>4293</v>
+      <c r="D200" s="3">
+        <v>6</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>896</v>
@@ -25133,8 +25118,8 @@
       <c r="C201" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D201" s="3" t="s">
-        <v>4293</v>
+      <c r="D201" s="3">
+        <v>6</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>122</v>
@@ -25183,8 +25168,8 @@
       <c r="C202" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D202" s="3" t="s">
-        <v>4284</v>
+      <c r="D202" s="3">
+        <v>7</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>33</v>
@@ -25238,7 +25223,7 @@
         <v>4274</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>215</v>
@@ -25346,7 +25331,7 @@
         <v>4274</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>293</v>
@@ -25453,8 +25438,8 @@
       <c r="C207" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D207" s="3" t="s">
-        <v>4284</v>
+      <c r="D207" s="3">
+        <v>7</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>33</v>
@@ -25507,8 +25492,8 @@
       <c r="C208" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D208" s="3" t="s">
-        <v>4284</v>
+      <c r="D208" s="3">
+        <v>7</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>302</v>
@@ -25555,8 +25540,8 @@
       <c r="C209" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D209" s="3" t="s">
-        <v>4293</v>
+      <c r="D209" s="3">
+        <v>6</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>122</v>
@@ -25610,7 +25595,7 @@
         <v>4274</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>494</v>
@@ -25664,7 +25649,7 @@
         <v>4274</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>326</v>
@@ -25717,8 +25702,8 @@
       <c r="C212" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D212" s="3" t="s">
-        <v>4285</v>
+      <c r="D212" s="3">
+        <v>4</v>
       </c>
       <c r="E212" s="3" t="s">
         <v>40</v>
@@ -25772,7 +25757,7 @@
         <v>4274</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>227</v>
@@ -25825,8 +25810,8 @@
       <c r="C214" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D214" s="3" t="s">
-        <v>4286</v>
+      <c r="D214" s="3">
+        <v>8</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>57</v>
@@ -25880,7 +25865,7 @@
         <v>4274</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>4313</v>
+        <v>4307</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>844</v>
@@ -25934,7 +25919,7 @@
         <v>4274</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>4309</v>
+        <v>4303</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>580</v>
@@ -25988,7 +25973,7 @@
         <v>4273</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>326</v>
@@ -26042,7 +26027,7 @@
         <v>4273</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E218" s="3" t="s">
         <v>242</v>
@@ -26096,7 +26081,7 @@
         <v>4274</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>4296</v>
+        <v>4290</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>188</v>
@@ -26149,8 +26134,8 @@
       <c r="C220" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D220" s="3" t="s">
-        <v>4284</v>
+      <c r="D220" s="3">
+        <v>7</v>
       </c>
       <c r="E220" s="3" t="s">
         <v>302</v>
@@ -26200,7 +26185,7 @@
         <v>4274</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>498</v>
@@ -26254,7 +26239,7 @@
         <v>4273</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>96</v>
@@ -26307,8 +26292,8 @@
       <c r="C223" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D223" s="3" t="s">
-        <v>4284</v>
+      <c r="D223" s="3">
+        <v>7</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>33</v>
@@ -26465,8 +26450,8 @@
       <c r="C226" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D226" s="3" t="s">
-        <v>4284</v>
+      <c r="D226" s="3">
+        <v>7</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>33</v>
@@ -26520,7 +26505,7 @@
         <v>4275</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>326</v>
@@ -26573,8 +26558,8 @@
       <c r="C228" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D228" s="3" t="s">
-        <v>4287</v>
+      <c r="D228" s="3">
+        <v>5</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>64</v>
@@ -26627,8 +26612,8 @@
       <c r="C229" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D229" s="3" t="s">
-        <v>4284</v>
+      <c r="D229" s="3">
+        <v>7</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>33</v>
@@ -26681,8 +26666,8 @@
       <c r="C230" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D230" s="3" t="s">
-        <v>4284</v>
+      <c r="D230" s="3">
+        <v>7</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>33</v>
@@ -26735,8 +26720,8 @@
       <c r="C231" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D231" s="3" t="s">
-        <v>4284</v>
+      <c r="D231" s="3">
+        <v>7</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>33</v>
@@ -26789,8 +26774,8 @@
       <c r="C232" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D232" s="3" t="s">
-        <v>4284</v>
+      <c r="D232" s="3">
+        <v>7</v>
       </c>
       <c r="E232" s="3" t="s">
         <v>33</v>
@@ -26843,8 +26828,8 @@
       <c r="C233" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D233" s="3" t="s">
-        <v>4284</v>
+      <c r="D233" s="3">
+        <v>7</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>33</v>
@@ -26897,8 +26882,8 @@
       <c r="C234" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D234" s="3" t="s">
-        <v>4289</v>
+      <c r="D234" s="3">
+        <v>9</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>86</v>
@@ -27006,7 +26991,7 @@
         <v>4274</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>4314</v>
+        <v>4308</v>
       </c>
       <c r="E236" s="3" t="s">
         <v>1037</v>
@@ -27059,8 +27044,8 @@
       <c r="C237" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D237" s="3" t="s">
-        <v>4284</v>
+      <c r="D237" s="3">
+        <v>7</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>33</v>
@@ -27113,8 +27098,8 @@
       <c r="C238" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D238" s="3" t="s">
-        <v>4285</v>
+      <c r="D238" s="3">
+        <v>4</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>40</v>
@@ -27168,7 +27153,7 @@
         <v>4274</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>96</v>
@@ -27222,7 +27207,7 @@
         <v>4274</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>566</v>
@@ -27276,7 +27261,7 @@
         <v>4275</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>263</v>
@@ -27329,8 +27314,8 @@
       <c r="C242" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D242" s="3" t="s">
-        <v>4293</v>
+      <c r="D242" s="3">
+        <v>6</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>122</v>
@@ -27384,7 +27369,7 @@
         <v>4273</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>222</v>
@@ -27544,7 +27529,7 @@
         <v>4273</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>4313</v>
+        <v>4307</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>844</v>
@@ -27598,7 +27583,7 @@
         <v>4274</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>4314</v>
+        <v>4308</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>1037</v>
@@ -27651,8 +27636,8 @@
       <c r="C248" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D248" s="3" t="s">
-        <v>4293</v>
+      <c r="D248" s="3">
+        <v>6</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>122</v>
@@ -27706,7 +27691,7 @@
         <v>4274</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>326</v>
@@ -27760,7 +27745,7 @@
         <v>4274</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>96</v>
@@ -27809,8 +27794,8 @@
       <c r="C251" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D251" s="3" t="s">
-        <v>4284</v>
+      <c r="D251" s="3">
+        <v>7</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>302</v>
@@ -27859,8 +27844,8 @@
       <c r="C252" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D252" s="3" t="s">
-        <v>4284</v>
+      <c r="D252" s="3">
+        <v>7</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>33</v>
@@ -27914,7 +27899,7 @@
         <v>4274</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>215</v>
@@ -27968,7 +27953,7 @@
         <v>4275</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>215</v>
@@ -28021,8 +28006,8 @@
       <c r="C255" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D255" s="3" t="s">
-        <v>4285</v>
+      <c r="D255" s="3">
+        <v>4</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>40</v>
@@ -28076,7 +28061,7 @@
         <v>4274</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>326</v>
@@ -28130,7 +28115,7 @@
         <v>4274</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>215</v>
@@ -28184,7 +28169,7 @@
         <v>4273</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E258" s="3" t="s">
         <v>215</v>
@@ -28238,7 +28223,7 @@
         <v>4273</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>498</v>
@@ -28292,7 +28277,7 @@
         <v>4274</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>4296</v>
+        <v>4290</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>188</v>
@@ -28346,7 +28331,7 @@
         <v>4274</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>494</v>
@@ -28400,7 +28385,7 @@
         <v>4273</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>118</v>
@@ -28453,8 +28438,8 @@
       <c r="C263" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D263" s="3" t="s">
-        <v>4287</v>
+      <c r="D263" s="3">
+        <v>5</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>64</v>
@@ -28508,7 +28493,7 @@
         <v>4273</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>498</v>
@@ -28562,7 +28547,7 @@
         <v>4275</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>118</v>
@@ -28616,7 +28601,7 @@
         <v>4276</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>227</v>
@@ -28670,7 +28655,7 @@
         <v>4274</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>566</v>
@@ -28723,8 +28708,8 @@
       <c r="C268" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D268" s="3" t="s">
-        <v>4284</v>
+      <c r="D268" s="3">
+        <v>7</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>33</v>
@@ -28777,8 +28762,8 @@
       <c r="C269" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D269" s="3" t="s">
-        <v>4287</v>
+      <c r="D269" s="3">
+        <v>5</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>64</v>
@@ -28831,8 +28816,8 @@
       <c r="C270" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D270" s="3" t="s">
-        <v>4293</v>
+      <c r="D270" s="3">
+        <v>6</v>
       </c>
       <c r="E270" s="3" t="s">
         <v>122</v>
@@ -28886,7 +28871,7 @@
         <v>4273</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>118</v>
@@ -28940,7 +28925,7 @@
         <v>4274</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E272" s="3" t="s">
         <v>566</v>
@@ -28994,7 +28979,7 @@
         <v>4274</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>227</v>
@@ -29048,7 +29033,7 @@
         <v>4273</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>118</v>
@@ -29101,8 +29086,8 @@
       <c r="C275" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D275" s="3" t="s">
-        <v>4293</v>
+      <c r="D275" s="3">
+        <v>6</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>122</v>
@@ -29264,7 +29249,7 @@
         <v>4274</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>118</v>
@@ -29317,8 +29302,8 @@
       <c r="C279" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D279" s="3" t="s">
-        <v>4284</v>
+      <c r="D279" s="3">
+        <v>7</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>33</v>
@@ -29371,8 +29356,8 @@
       <c r="C280" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D280" s="3" t="s">
-        <v>4284</v>
+      <c r="D280" s="3">
+        <v>7</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>33</v>
@@ -29426,7 +29411,7 @@
         <v>4274</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E281" s="3" t="s">
         <v>242</v>
@@ -29527,8 +29512,8 @@
       <c r="C283" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D283" s="3" t="s">
-        <v>4287</v>
+      <c r="D283" s="3">
+        <v>5</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>64</v>
@@ -29582,7 +29567,7 @@
         <v>4274</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>4309</v>
+        <v>4303</v>
       </c>
       <c r="E284" s="3" t="s">
         <v>580</v>
@@ -29635,8 +29620,8 @@
       <c r="C285" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D285" s="3" t="s">
-        <v>4285</v>
+      <c r="D285" s="3">
+        <v>4</v>
       </c>
       <c r="E285" s="3" t="s">
         <v>40</v>
@@ -29690,7 +29675,7 @@
         <v>4274</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>227</v>
@@ -29744,7 +29729,7 @@
         <v>4274</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E287" s="3" t="s">
         <v>333</v>
@@ -29798,7 +29783,7 @@
         <v>4275</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E288" s="3" t="s">
         <v>96</v>
@@ -29852,7 +29837,7 @@
         <v>4274</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E289" s="3" t="s">
         <v>215</v>
@@ -29906,7 +29891,7 @@
         <v>4274</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>4315</v>
+        <v>4309</v>
       </c>
       <c r="E290" s="3" t="s">
         <v>1225</v>
@@ -29960,7 +29945,7 @@
         <v>4274</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E291" s="3" t="s">
         <v>293</v>
@@ -30014,7 +29999,7 @@
         <v>4274</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E292" s="3" t="s">
         <v>227</v>
@@ -30068,7 +30053,7 @@
         <v>4274</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E293" s="3" t="s">
         <v>215</v>
@@ -30122,7 +30107,7 @@
         <v>4273</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E294" s="3" t="s">
         <v>326</v>
@@ -30175,8 +30160,8 @@
       <c r="C295" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D295" s="3" t="s">
-        <v>4285</v>
+      <c r="D295" s="3">
+        <v>4</v>
       </c>
       <c r="E295" s="3" t="s">
         <v>40</v>
@@ -30229,8 +30214,8 @@
       <c r="C296" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D296" s="3" t="s">
-        <v>4293</v>
+      <c r="D296" s="3">
+        <v>6</v>
       </c>
       <c r="E296" s="3" t="s">
         <v>122</v>
@@ -30283,8 +30268,8 @@
       <c r="C297" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D297" s="3" t="s">
-        <v>4287</v>
+      <c r="D297" s="3">
+        <v>5</v>
       </c>
       <c r="E297" s="3" t="s">
         <v>64</v>
@@ -30338,7 +30323,7 @@
         <v>4274</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E298" s="3" t="s">
         <v>215</v>
@@ -30391,8 +30376,8 @@
       <c r="C299" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D299" s="3" t="s">
-        <v>4285</v>
+      <c r="D299" s="3">
+        <v>4</v>
       </c>
       <c r="E299" s="3" t="s">
         <v>40</v>
@@ -30445,8 +30430,8 @@
       <c r="C300" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D300" s="3" t="s">
-        <v>4289</v>
+      <c r="D300" s="3">
+        <v>9</v>
       </c>
       <c r="E300" s="3" t="s">
         <v>86</v>
@@ -30499,8 +30484,8 @@
       <c r="C301" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D301" s="3" t="s">
-        <v>4293</v>
+      <c r="D301" s="3">
+        <v>6</v>
       </c>
       <c r="E301" s="3" t="s">
         <v>122</v>
@@ -30553,8 +30538,8 @@
       <c r="C302" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D302" s="3" t="s">
-        <v>4293</v>
+      <c r="D302" s="3">
+        <v>6</v>
       </c>
       <c r="E302" s="3" t="s">
         <v>122</v>
@@ -30655,8 +30640,8 @@
       <c r="C304" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D304" s="3" t="s">
-        <v>4289</v>
+      <c r="D304" s="3">
+        <v>9</v>
       </c>
       <c r="E304" s="3" t="s">
         <v>86</v>
@@ -30709,8 +30694,8 @@
       <c r="C305" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D305" s="3" t="s">
-        <v>4284</v>
+      <c r="D305" s="3">
+        <v>7</v>
       </c>
       <c r="E305" s="3" t="s">
         <v>33</v>
@@ -30760,7 +30745,7 @@
         <v>4274</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>4314</v>
+        <v>4308</v>
       </c>
       <c r="E306" s="3" t="s">
         <v>1037</v>
@@ -30814,7 +30799,7 @@
         <v>4274</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E307" s="3" t="s">
         <v>215</v>
@@ -30868,7 +30853,7 @@
         <v>4274</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E308" s="3" t="s">
         <v>498</v>
@@ -30921,8 +30906,8 @@
       <c r="C309" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D309" s="3" t="s">
-        <v>4286</v>
+      <c r="D309" s="3">
+        <v>8</v>
       </c>
       <c r="E309" s="3" t="s">
         <v>57</v>
@@ -31029,8 +31014,8 @@
       <c r="C311" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D311" s="3" t="s">
-        <v>4284</v>
+      <c r="D311" s="3">
+        <v>7</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>33</v>
@@ -31084,7 +31069,7 @@
         <v>4273</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E312" s="3" t="s">
         <v>215</v>
@@ -31176,7 +31161,7 @@
         <v>4274</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E314" s="3" t="s">
         <v>215</v>
@@ -31230,7 +31215,7 @@
         <v>4276</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E315" s="3" t="s">
         <v>498</v>
@@ -31284,7 +31269,7 @@
         <v>4274</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>1315</v>
@@ -31333,8 +31318,8 @@
       <c r="C317" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D317" s="3" t="s">
-        <v>4293</v>
+      <c r="D317" s="3">
+        <v>6</v>
       </c>
       <c r="E317" s="3" t="s">
         <v>122</v>
@@ -31600,7 +31585,7 @@
         <v>4273</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E322" s="3" t="s">
         <v>227</v>
@@ -31654,7 +31639,7 @@
         <v>4274</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E323" s="3" t="s">
         <v>498</v>
@@ -31704,7 +31689,7 @@
         <v>4274</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>215</v>
@@ -31757,8 +31742,8 @@
       <c r="C325" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D325" s="3" t="s">
-        <v>4286</v>
+      <c r="D325" s="3">
+        <v>8</v>
       </c>
       <c r="E325" s="3" t="s">
         <v>57</v>
@@ -31807,8 +31792,8 @@
       <c r="C326" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D326" s="3" t="s">
-        <v>4286</v>
+      <c r="D326" s="3">
+        <v>8</v>
       </c>
       <c r="E326" s="3" t="s">
         <v>57</v>
@@ -31910,7 +31895,7 @@
         <v>4274</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>4316</v>
+        <v>4310</v>
       </c>
       <c r="E328" s="3" t="s">
         <v>1348</v>
@@ -31964,7 +31949,7 @@
         <v>4274</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>4317</v>
+        <v>4311</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>1352</v>
@@ -32017,8 +32002,8 @@
       <c r="C330" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D330" s="3" t="s">
-        <v>4284</v>
+      <c r="D330" s="3">
+        <v>7</v>
       </c>
       <c r="E330" s="3" t="s">
         <v>33</v>
@@ -32071,8 +32056,8 @@
       <c r="C331" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D331" s="3" t="s">
-        <v>4286</v>
+      <c r="D331" s="3">
+        <v>8</v>
       </c>
       <c r="E331" s="3" t="s">
         <v>57</v>
@@ -32126,7 +32111,7 @@
         <v>4276</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E332" s="3" t="s">
         <v>326</v>
@@ -32233,8 +32218,8 @@
       <c r="C334" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D334" s="3" t="s">
-        <v>4287</v>
+      <c r="D334" s="3">
+        <v>5</v>
       </c>
       <c r="E334" s="3" t="s">
         <v>64</v>
@@ -32288,7 +32273,7 @@
         <v>4275</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E335" s="3" t="s">
         <v>566</v>
@@ -32341,8 +32326,8 @@
       <c r="C336" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D336" s="3" t="s">
-        <v>4293</v>
+      <c r="D336" s="3">
+        <v>6</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>122</v>
@@ -32396,7 +32381,7 @@
         <v>4274</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E337" s="3" t="s">
         <v>498</v>
@@ -32449,8 +32434,8 @@
       <c r="C338" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D338" s="3" t="s">
-        <v>4286</v>
+      <c r="D338" s="3">
+        <v>8</v>
       </c>
       <c r="E338" s="3" t="s">
         <v>57</v>
@@ -32504,7 +32489,7 @@
         <v>4274</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E339" s="3" t="s">
         <v>242</v>
@@ -32558,7 +32543,7 @@
         <v>4275</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>498</v>
@@ -32611,8 +32596,8 @@
       <c r="C341" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D341" s="3" t="s">
-        <v>4285</v>
+      <c r="D341" s="3">
+        <v>4</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>40</v>
@@ -32666,7 +32651,7 @@
         <v>4275</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E342" s="3" t="s">
         <v>498</v>
@@ -32719,8 +32704,8 @@
       <c r="C343" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D343" s="3" t="s">
-        <v>4293</v>
+      <c r="D343" s="3">
+        <v>6</v>
       </c>
       <c r="E343" s="3" t="s">
         <v>122</v>
@@ -32828,7 +32813,7 @@
         <v>4273</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E345" s="3" t="s">
         <v>215</v>
@@ -32882,7 +32867,7 @@
         <v>4274</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E346" s="3" t="s">
         <v>227</v>
@@ -32936,7 +32921,7 @@
         <v>4274</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>494</v>
@@ -32990,7 +32975,7 @@
         <v>4274</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>4307</v>
+        <v>4301</v>
       </c>
       <c r="E348" s="3" t="s">
         <v>556</v>
@@ -33044,7 +33029,7 @@
         <v>4273</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E349" s="3" t="s">
         <v>326</v>
@@ -33098,7 +33083,7 @@
         <v>4274</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>333</v>
@@ -33149,8 +33134,8 @@
       <c r="C351" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D351" s="3" t="s">
-        <v>4287</v>
+      <c r="D351" s="3">
+        <v>5</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>64</v>
@@ -33203,8 +33188,8 @@
       <c r="C352" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D352" s="3" t="s">
-        <v>4284</v>
+      <c r="D352" s="3">
+        <v>7</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>33</v>
@@ -33258,7 +33243,7 @@
         <v>4274</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>252</v>
@@ -33312,7 +33297,7 @@
         <v>4274</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>498</v>
@@ -33365,8 +33350,8 @@
       <c r="C355" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D355" s="3" t="s">
-        <v>4287</v>
+      <c r="D355" s="3">
+        <v>5</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>64</v>
@@ -33416,7 +33401,7 @@
         <v>4275</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>222</v>
@@ -33470,7 +33455,7 @@
         <v>4274</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>333</v>
@@ -33523,8 +33508,8 @@
       <c r="C358" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D358" s="3" t="s">
-        <v>4287</v>
+      <c r="D358" s="3">
+        <v>5</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>64</v>
@@ -33578,7 +33563,7 @@
         <v>4273</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E359" s="3" t="s">
         <v>222</v>
@@ -33631,8 +33616,8 @@
       <c r="C360" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D360" s="3" t="s">
-        <v>4289</v>
+      <c r="D360" s="3">
+        <v>9</v>
       </c>
       <c r="E360" s="3" t="s">
         <v>86</v>
@@ -33686,7 +33671,7 @@
         <v>4274</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E361" s="3" t="s">
         <v>498</v>
@@ -33740,7 +33725,7 @@
         <v>4274</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E362" s="3" t="s">
         <v>263</v>
@@ -33790,7 +33775,7 @@
         <v>4274</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E363" s="3" t="s">
         <v>293</v>
@@ -33843,8 +33828,8 @@
       <c r="C364" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D364" s="3" t="s">
-        <v>4284</v>
+      <c r="D364" s="3">
+        <v>7</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>33</v>
@@ -33898,7 +33883,7 @@
         <v>4276</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E365" s="3" t="s">
         <v>222</v>
@@ -33952,7 +33937,7 @@
         <v>4273</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>252</v>
@@ -34269,8 +34254,8 @@
       <c r="C373" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D373" s="3" t="s">
-        <v>4287</v>
+      <c r="D373" s="3">
+        <v>5</v>
       </c>
       <c r="E373" s="3" t="s">
         <v>64</v>
@@ -34323,8 +34308,8 @@
       <c r="C374" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D374" s="3" t="s">
-        <v>4287</v>
+      <c r="D374" s="3">
+        <v>5</v>
       </c>
       <c r="E374" s="3" t="s">
         <v>64</v>
@@ -34378,7 +34363,7 @@
         <v>4274</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>227</v>
@@ -34432,7 +34417,7 @@
         <v>4274</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>498</v>
@@ -34482,7 +34467,7 @@
         <v>4274</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>263</v>
@@ -34535,8 +34520,8 @@
       <c r="C378" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D378" s="3" t="s">
-        <v>4293</v>
+      <c r="D378" s="3">
+        <v>6</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>896</v>
@@ -34584,7 +34569,7 @@
         <v>4274</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E379" s="3" t="s">
         <v>227</v>
@@ -34638,7 +34623,7 @@
         <v>4274</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E380" s="3" t="s">
         <v>227</v>
@@ -34741,8 +34726,8 @@
       <c r="C382" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D382" s="3" t="s">
-        <v>4285</v>
+      <c r="D382" s="3">
+        <v>4</v>
       </c>
       <c r="E382" s="3" t="s">
         <v>40</v>
@@ -34795,8 +34780,8 @@
       <c r="C383" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D383" s="3" t="s">
-        <v>4286</v>
+      <c r="D383" s="3">
+        <v>8</v>
       </c>
       <c r="E383" s="3" t="s">
         <v>57</v>
@@ -34850,7 +34835,7 @@
         <v>4274</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E384" s="3" t="s">
         <v>215</v>
@@ -34904,7 +34889,7 @@
         <v>4273</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>4309</v>
+        <v>4303</v>
       </c>
       <c r="E385" s="3" t="s">
         <v>580</v>
@@ -34958,7 +34943,7 @@
         <v>4275</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E386" s="3" t="s">
         <v>498</v>
@@ -35012,7 +34997,7 @@
         <v>4273</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E387" s="3" t="s">
         <v>177</v>
@@ -35066,7 +35051,7 @@
         <v>4274</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E388" s="3" t="s">
         <v>1533</v>
@@ -35165,8 +35150,8 @@
       <c r="C390" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D390" s="3" t="s">
-        <v>4289</v>
+      <c r="D390" s="3">
+        <v>9</v>
       </c>
       <c r="E390" s="3" t="s">
         <v>86</v>
@@ -35220,7 +35205,7 @@
         <v>4275</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E391" s="3" t="s">
         <v>96</v>
@@ -35274,7 +35259,7 @@
         <v>4273</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E392" s="3" t="s">
         <v>263</v>
@@ -35382,7 +35367,7 @@
         <v>4274</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E394" s="3" t="s">
         <v>96</v>
@@ -35435,8 +35420,8 @@
       <c r="C395" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D395" s="3" t="s">
-        <v>4293</v>
+      <c r="D395" s="3">
+        <v>6</v>
       </c>
       <c r="E395" s="3" t="s">
         <v>122</v>
@@ -35490,7 +35475,7 @@
         <v>4273</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E396" s="3" t="s">
         <v>215</v>
@@ -35543,8 +35528,8 @@
       <c r="C397" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D397" s="3" t="s">
-        <v>4289</v>
+      <c r="D397" s="3">
+        <v>9</v>
       </c>
       <c r="E397" s="3" t="s">
         <v>86</v>
@@ -35597,8 +35582,8 @@
       <c r="C398" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D398" s="3" t="s">
-        <v>4285</v>
+      <c r="D398" s="3">
+        <v>4</v>
       </c>
       <c r="E398" s="3" t="s">
         <v>40</v>
@@ -35652,7 +35637,7 @@
         <v>4274</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>4318</v>
+        <v>4312</v>
       </c>
       <c r="E399" s="3" t="s">
         <v>1566</v>
@@ -35759,8 +35744,8 @@
       <c r="C401" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D401" s="3" t="s">
-        <v>4287</v>
+      <c r="D401" s="3">
+        <v>5</v>
       </c>
       <c r="E401" s="3" t="s">
         <v>64</v>
@@ -35814,7 +35799,7 @@
         <v>4274</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E402" s="3" t="s">
         <v>494</v>
@@ -35970,7 +35955,7 @@
         <v>4274</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E405" s="3" t="s">
         <v>263</v>
@@ -36022,7 +36007,7 @@
         <v>4276</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E406" s="3" t="s">
         <v>215</v>
@@ -36126,7 +36111,7 @@
         <v>4274</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E408" s="3" t="s">
         <v>498</v>
@@ -36180,7 +36165,7 @@
         <v>4275</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E409" s="3" t="s">
         <v>252</v>
@@ -36234,7 +36219,7 @@
         <v>4274</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E410" s="3" t="s">
         <v>498</v>
@@ -36288,7 +36273,7 @@
         <v>4274</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E411" s="3" t="s">
         <v>498</v>
@@ -36336,7 +36321,7 @@
         <v>4273</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E412" s="3" t="s">
         <v>96</v>
@@ -36390,7 +36375,7 @@
         <v>4273</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E413" s="3" t="s">
         <v>326</v>
@@ -36443,8 +36428,8 @@
       <c r="C414" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D414" s="3" t="s">
-        <v>4286</v>
+      <c r="D414" s="3">
+        <v>8</v>
       </c>
       <c r="E414" s="3" t="s">
         <v>57</v>
@@ -36498,7 +36483,7 @@
         <v>4274</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E415" s="3" t="s">
         <v>333</v>
@@ -36552,7 +36537,7 @@
         <v>4273</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E416" s="3" t="s">
         <v>263</v>
@@ -36606,7 +36591,7 @@
         <v>4274</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E417" s="3" t="s">
         <v>498</v>
@@ -36659,8 +36644,8 @@
       <c r="C418" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D418" s="3" t="s">
-        <v>4285</v>
+      <c r="D418" s="3">
+        <v>4</v>
       </c>
       <c r="E418" s="3" t="s">
         <v>40</v>
@@ -36713,8 +36698,8 @@
       <c r="C419" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D419" s="3" t="s">
-        <v>4284</v>
+      <c r="D419" s="3">
+        <v>7</v>
       </c>
       <c r="E419" s="3" t="s">
         <v>33</v>
@@ -36768,7 +36753,7 @@
         <v>4273</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E420" s="3" t="s">
         <v>498</v>
@@ -36821,8 +36806,8 @@
       <c r="C421" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D421" s="3" t="s">
-        <v>4293</v>
+      <c r="D421" s="3">
+        <v>6</v>
       </c>
       <c r="E421" s="3" t="s">
         <v>122</v>
@@ -36875,8 +36860,8 @@
       <c r="C422" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D422" s="3" t="s">
-        <v>4285</v>
+      <c r="D422" s="3">
+        <v>4</v>
       </c>
       <c r="E422" s="3" t="s">
         <v>40</v>
@@ -36930,7 +36915,7 @@
         <v>4274</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E423" s="3" t="s">
         <v>222</v>
@@ -36981,8 +36966,8 @@
       <c r="C424" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D424" s="3" t="s">
-        <v>4293</v>
+      <c r="D424" s="3">
+        <v>6</v>
       </c>
       <c r="E424" s="3" t="s">
         <v>122</v>
@@ -37036,7 +37021,7 @@
         <v>4273</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E425" s="3" t="s">
         <v>118</v>
@@ -37088,7 +37073,7 @@
         <v>4275</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E426" s="3" t="s">
         <v>222</v>
@@ -37138,7 +37123,7 @@
         <v>4273</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E427" s="3" t="s">
         <v>227</v>
@@ -37191,8 +37176,8 @@
       <c r="C428" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D428" s="3" t="s">
-        <v>4289</v>
+      <c r="D428" s="3">
+        <v>9</v>
       </c>
       <c r="E428" s="3" t="s">
         <v>86</v>
@@ -37245,8 +37230,8 @@
       <c r="C429" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D429" s="3" t="s">
-        <v>4287</v>
+      <c r="D429" s="3">
+        <v>5</v>
       </c>
       <c r="E429" s="3" t="s">
         <v>64</v>
@@ -37300,7 +37285,7 @@
         <v>4274</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E430" s="3" t="s">
         <v>222</v>
@@ -37353,8 +37338,8 @@
       <c r="C431" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D431" s="3" t="s">
-        <v>4289</v>
+      <c r="D431" s="3">
+        <v>9</v>
       </c>
       <c r="E431" s="3" t="s">
         <v>86</v>
@@ -37408,7 +37393,7 @@
         <v>4274</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E432" s="3" t="s">
         <v>130</v>
@@ -37462,7 +37447,7 @@
         <v>4274</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E433" s="3" t="s">
         <v>215</v>
@@ -37516,7 +37501,7 @@
         <v>4274</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>4319</v>
+        <v>4313</v>
       </c>
       <c r="E434" s="3" t="s">
         <v>1643</v>
@@ -37569,8 +37554,8 @@
       <c r="C435" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D435" s="3" t="s">
-        <v>4286</v>
+      <c r="D435" s="3">
+        <v>8</v>
       </c>
       <c r="E435" s="3" t="s">
         <v>57</v>
@@ -37623,8 +37608,8 @@
       <c r="C436" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D436" s="3" t="s">
-        <v>4293</v>
+      <c r="D436" s="3">
+        <v>6</v>
       </c>
       <c r="E436" s="3" t="s">
         <v>122</v>
@@ -37674,7 +37659,7 @@
         <v>4274</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E437" s="3" t="s">
         <v>263</v>
@@ -37724,7 +37709,7 @@
         <v>4275</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E438" s="3" t="s">
         <v>263</v>
@@ -37774,7 +37759,7 @@
         <v>4276</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E439" s="3" t="s">
         <v>263</v>
@@ -37828,7 +37813,7 @@
         <v>4273</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E440" s="3" t="s">
         <v>498</v>
@@ -37879,8 +37864,8 @@
       <c r="C441" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D441" s="3" t="s">
-        <v>4287</v>
+      <c r="D441" s="3">
+        <v>5</v>
       </c>
       <c r="E441" s="3" t="s">
         <v>64</v>
@@ -37934,7 +37919,7 @@
         <v>4273</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E442" s="3" t="s">
         <v>96</v>
@@ -37983,8 +37968,8 @@
       <c r="C443" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D443" s="3" t="s">
-        <v>4293</v>
+      <c r="D443" s="3">
+        <v>6</v>
       </c>
       <c r="E443" s="3" t="s">
         <v>122</v>
@@ -38038,7 +38023,7 @@
         <v>4273</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>4296</v>
+        <v>4290</v>
       </c>
       <c r="E444" s="3" t="s">
         <v>188</v>
@@ -38087,8 +38072,8 @@
       <c r="C445" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D445" s="3" t="s">
-        <v>4289</v>
+      <c r="D445" s="3">
+        <v>9</v>
       </c>
       <c r="E445" s="3" t="s">
         <v>86</v>
@@ -38196,7 +38181,7 @@
         <v>4274</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E447" s="3" t="s">
         <v>215</v>
@@ -38247,8 +38232,8 @@
       <c r="C448" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D448" s="3" t="s">
-        <v>4284</v>
+      <c r="D448" s="3">
+        <v>7</v>
       </c>
       <c r="E448" s="3" t="s">
         <v>302</v>
@@ -38298,7 +38283,7 @@
         <v>4276</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E449" s="3" t="s">
         <v>263</v>
@@ -38348,7 +38333,7 @@
         <v>4274</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E450" s="3" t="s">
         <v>215</v>
@@ -38402,7 +38387,7 @@
         <v>4275</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E451" s="3" t="s">
         <v>333</v>
@@ -38455,8 +38440,8 @@
       <c r="C452" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D452" s="3" t="s">
-        <v>4284</v>
+      <c r="D452" s="3">
+        <v>7</v>
       </c>
       <c r="E452" s="3" t="s">
         <v>302</v>
@@ -38505,8 +38490,8 @@
       <c r="C453" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D453" s="3" t="s">
-        <v>4286</v>
+      <c r="D453" s="3">
+        <v>8</v>
       </c>
       <c r="E453" s="3" t="s">
         <v>57</v>
@@ -38556,7 +38541,7 @@
         <v>4273</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E454" s="3" t="s">
         <v>494</v>
@@ -38606,7 +38591,7 @@
         <v>4274</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E455" s="3" t="s">
         <v>326</v>
@@ -38660,7 +38645,7 @@
         <v>4274</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E456" s="3" t="s">
         <v>263</v>
@@ -38712,7 +38697,7 @@
         <v>4273</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E457" s="3" t="s">
         <v>177</v>
@@ -38762,7 +38747,7 @@
         <v>4273</v>
       </c>
       <c r="D458" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E458" s="3" t="s">
         <v>263</v>
@@ -38816,7 +38801,7 @@
         <v>4274</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E459" s="3" t="s">
         <v>498</v>
@@ -38866,7 +38851,7 @@
         <v>4275</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E460" s="3" t="s">
         <v>333</v>
@@ -39024,7 +39009,7 @@
         <v>4274</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E463" s="3" t="s">
         <v>498</v>
@@ -39077,8 +39062,8 @@
       <c r="C464" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D464" s="3" t="s">
-        <v>4287</v>
+      <c r="D464" s="3">
+        <v>5</v>
       </c>
       <c r="E464" s="3" t="s">
         <v>64</v>
@@ -39132,7 +39117,7 @@
         <v>4273</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E465" s="3" t="s">
         <v>215</v>
@@ -39185,8 +39170,8 @@
       <c r="C466" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D466" s="3" t="s">
-        <v>4287</v>
+      <c r="D466" s="3">
+        <v>5</v>
       </c>
       <c r="E466" s="3" t="s">
         <v>64</v>
@@ -39239,8 +39224,8 @@
       <c r="C467" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D467" s="3" t="s">
-        <v>4284</v>
+      <c r="D467" s="3">
+        <v>7</v>
       </c>
       <c r="E467" s="3" t="s">
         <v>33</v>
@@ -39290,7 +39275,7 @@
         <v>4274</v>
       </c>
       <c r="D468" s="3" t="s">
-        <v>4317</v>
+        <v>4311</v>
       </c>
       <c r="E468" s="3" t="s">
         <v>1352</v>
@@ -39340,7 +39325,7 @@
         <v>4274</v>
       </c>
       <c r="D469" s="3" t="s">
-        <v>4320</v>
+        <v>4314</v>
       </c>
       <c r="E469" s="3" t="s">
         <v>1739</v>
@@ -39394,7 +39379,7 @@
         <v>4274</v>
       </c>
       <c r="D470" s="3" t="s">
-        <v>4310</v>
+        <v>4304</v>
       </c>
       <c r="E470" s="3" t="s">
         <v>613</v>
@@ -39444,7 +39429,7 @@
         <v>4275</v>
       </c>
       <c r="D471" s="3" t="s">
-        <v>4310</v>
+        <v>4304</v>
       </c>
       <c r="E471" s="3" t="s">
         <v>613</v>
@@ -39497,8 +39482,8 @@
       <c r="C472" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D472" s="3" t="s">
-        <v>4289</v>
+      <c r="D472" s="3">
+        <v>9</v>
       </c>
       <c r="E472" s="3" t="s">
         <v>86</v>
@@ -39547,8 +39532,8 @@
       <c r="C473" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D473" s="3" t="s">
-        <v>4286</v>
+      <c r="D473" s="3">
+        <v>8</v>
       </c>
       <c r="E473" s="3" t="s">
         <v>57</v>
@@ -39601,8 +39586,8 @@
       <c r="C474" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D474" s="3" t="s">
-        <v>4293</v>
+      <c r="D474" s="3">
+        <v>6</v>
       </c>
       <c r="E474" s="3" t="s">
         <v>122</v>
@@ -39710,7 +39695,7 @@
         <v>4276</v>
       </c>
       <c r="D476" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E476" s="3" t="s">
         <v>498</v>
@@ -39763,8 +39748,8 @@
       <c r="C477" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D477" s="3" t="s">
-        <v>4293</v>
+      <c r="D477" s="3">
+        <v>6</v>
       </c>
       <c r="E477" s="3" t="s">
         <v>122</v>
@@ -39870,7 +39855,7 @@
         <v>4274</v>
       </c>
       <c r="D479" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E479" s="3" t="s">
         <v>498</v>
@@ -39978,7 +39963,7 @@
         <v>4274</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E481" s="3" t="s">
         <v>96</v>
@@ -40076,7 +40061,7 @@
         <v>4274</v>
       </c>
       <c r="D483" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E483" s="3" t="s">
         <v>222</v>
@@ -40129,8 +40114,8 @@
       <c r="C484" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D484" s="3" t="s">
-        <v>4286</v>
+      <c r="D484" s="3">
+        <v>8</v>
       </c>
       <c r="E484" s="3" t="s">
         <v>57</v>
@@ -40238,7 +40223,7 @@
         <v>4273</v>
       </c>
       <c r="D486" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E486" s="3" t="s">
         <v>498</v>
@@ -40345,8 +40330,8 @@
       <c r="C488" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D488" s="3" t="s">
-        <v>4284</v>
+      <c r="D488" s="3">
+        <v>7</v>
       </c>
       <c r="E488" s="3" t="s">
         <v>33</v>
@@ -40400,7 +40385,7 @@
         <v>4275</v>
       </c>
       <c r="D489" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E489" s="3" t="s">
         <v>1797</v>
@@ -40454,7 +40439,7 @@
         <v>4274</v>
       </c>
       <c r="D490" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E490" s="3" t="s">
         <v>494</v>
@@ -40504,7 +40489,7 @@
         <v>4274</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E491" s="3" t="s">
         <v>326</v>
@@ -40558,7 +40543,7 @@
         <v>4275</v>
       </c>
       <c r="D492" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E492" s="3" t="s">
         <v>252</v>
@@ -40611,8 +40596,8 @@
       <c r="C493" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D493" s="3" t="s">
-        <v>4285</v>
+      <c r="D493" s="3">
+        <v>4</v>
       </c>
       <c r="E493" s="3" t="s">
         <v>40</v>
@@ -40666,7 +40651,7 @@
         <v>4275</v>
       </c>
       <c r="D494" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E494" s="3" t="s">
         <v>215</v>
@@ -40719,8 +40704,8 @@
       <c r="C495" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D495" s="3" t="s">
-        <v>4293</v>
+      <c r="D495" s="3">
+        <v>6</v>
       </c>
       <c r="E495" s="3" t="s">
         <v>122</v>
@@ -40774,7 +40759,7 @@
         <v>4273</v>
       </c>
       <c r="D496" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E496" s="3" t="s">
         <v>215</v>
@@ -40827,8 +40812,8 @@
       <c r="C497" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D497" s="3" t="s">
-        <v>4293</v>
+      <c r="D497" s="3">
+        <v>6</v>
       </c>
       <c r="E497" s="3" t="s">
         <v>122</v>
@@ -40882,7 +40867,7 @@
         <v>4274</v>
       </c>
       <c r="D498" s="3" t="s">
-        <v>4317</v>
+        <v>4311</v>
       </c>
       <c r="E498" s="3" t="s">
         <v>1352</v>
@@ -40936,7 +40921,7 @@
         <v>4274</v>
       </c>
       <c r="D499" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E499" s="3" t="s">
         <v>498</v>
@@ -40990,7 +40975,7 @@
         <v>4273</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E500" s="3" t="s">
         <v>227</v>
@@ -41043,8 +41028,8 @@
       <c r="C501" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D501" s="3" t="s">
-        <v>4284</v>
+      <c r="D501" s="3">
+        <v>7</v>
       </c>
       <c r="E501" s="3" t="s">
         <v>302</v>
@@ -41091,8 +41076,8 @@
       <c r="C502" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D502" s="3" t="s">
-        <v>4284</v>
+      <c r="D502" s="3">
+        <v>7</v>
       </c>
       <c r="E502" s="3" t="s">
         <v>302</v>
@@ -41140,7 +41125,7 @@
         <v>4274</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E503" s="3" t="s">
         <v>498</v>
@@ -41190,7 +41175,7 @@
         <v>4275</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E504" s="3" t="s">
         <v>498</v>
@@ -41244,7 +41229,7 @@
         <v>4274</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E505" s="3" t="s">
         <v>494</v>
@@ -41297,8 +41282,8 @@
       <c r="C506" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D506" s="3" t="s">
-        <v>4287</v>
+      <c r="D506" s="3">
+        <v>5</v>
       </c>
       <c r="E506" s="3" t="s">
         <v>64</v>
@@ -41352,7 +41337,7 @@
         <v>4274</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>4312</v>
+        <v>4306</v>
       </c>
       <c r="E507" s="3" t="s">
         <v>749</v>
@@ -41406,7 +41391,7 @@
         <v>4274</v>
       </c>
       <c r="D508" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E508" s="3" t="s">
         <v>118</v>
@@ -41459,8 +41444,8 @@
       <c r="C509" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D509" s="3" t="s">
-        <v>4284</v>
+      <c r="D509" s="3">
+        <v>7</v>
       </c>
       <c r="E509" s="3" t="s">
         <v>33</v>
@@ -41514,7 +41499,7 @@
         <v>4273</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E510" s="3" t="s">
         <v>498</v>
@@ -41567,8 +41552,8 @@
       <c r="C511" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D511" s="3" t="s">
-        <v>4284</v>
+      <c r="D511" s="3">
+        <v>7</v>
       </c>
       <c r="E511" s="3" t="s">
         <v>33</v>
@@ -41621,8 +41606,8 @@
       <c r="C512" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D512" s="3" t="s">
-        <v>4284</v>
+      <c r="D512" s="3">
+        <v>7</v>
       </c>
       <c r="E512" s="3" t="s">
         <v>33</v>
@@ -41676,7 +41661,7 @@
         <v>4273</v>
       </c>
       <c r="D513" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E513" s="3" t="s">
         <v>222</v>
@@ -41730,7 +41715,7 @@
         <v>4274</v>
       </c>
       <c r="D514" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E514" s="3" t="s">
         <v>130</v>
@@ -41784,7 +41769,7 @@
         <v>4274</v>
       </c>
       <c r="D515" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E515" s="3" t="s">
         <v>326</v>
@@ -41833,8 +41818,8 @@
       <c r="C516" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D516" s="3" t="s">
-        <v>4286</v>
+      <c r="D516" s="3">
+        <v>8</v>
       </c>
       <c r="E516" s="3" t="s">
         <v>57</v>
@@ -41888,7 +41873,7 @@
         <v>4274</v>
       </c>
       <c r="D517" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E517" s="3" t="s">
         <v>227</v>
@@ -41942,7 +41927,7 @@
         <v>4274</v>
       </c>
       <c r="D518" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E518" s="3" t="s">
         <v>263</v>
@@ -41995,8 +41980,8 @@
       <c r="C519" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D519" s="3" t="s">
-        <v>4287</v>
+      <c r="D519" s="3">
+        <v>5</v>
       </c>
       <c r="E519" s="3" t="s">
         <v>64</v>
@@ -42049,8 +42034,8 @@
       <c r="C520" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D520" s="3" t="s">
-        <v>4287</v>
+      <c r="D520" s="3">
+        <v>5</v>
       </c>
       <c r="E520" s="3" t="s">
         <v>64</v>
@@ -42103,8 +42088,8 @@
       <c r="C521" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D521" s="3" t="s">
-        <v>4285</v>
+      <c r="D521" s="3">
+        <v>4</v>
       </c>
       <c r="E521" s="3" t="s">
         <v>40</v>
@@ -42262,7 +42247,7 @@
         <v>4273</v>
       </c>
       <c r="D524" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E524" s="3" t="s">
         <v>96</v>
@@ -42316,7 +42301,7 @@
         <v>4274</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E525" s="3" t="s">
         <v>227</v>
@@ -42422,7 +42407,7 @@
         <v>4274</v>
       </c>
       <c r="D527" s="3" t="s">
-        <v>4321</v>
+        <v>4315</v>
       </c>
       <c r="E527" s="3" t="s">
         <v>1914</v>
@@ -42476,7 +42461,7 @@
         <v>4274</v>
       </c>
       <c r="D528" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E528" s="3" t="s">
         <v>227</v>
@@ -42530,7 +42515,7 @@
         <v>4274</v>
       </c>
       <c r="D529" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E529" s="3" t="s">
         <v>1533</v>
@@ -42632,7 +42617,7 @@
         <v>4274</v>
       </c>
       <c r="D531" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E531" s="3" t="s">
         <v>130</v>
@@ -42682,7 +42667,7 @@
         <v>4276</v>
       </c>
       <c r="D532" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E532" s="3" t="s">
         <v>215</v>
@@ -42786,7 +42771,7 @@
         <v>4273</v>
       </c>
       <c r="D534" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E534" s="3" t="s">
         <v>326</v>
@@ -42839,8 +42824,8 @@
       <c r="C535" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D535" s="3" t="s">
-        <v>4286</v>
+      <c r="D535" s="3">
+        <v>8</v>
       </c>
       <c r="E535" s="3" t="s">
         <v>57</v>
@@ -42893,8 +42878,8 @@
       <c r="C536" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D536" s="3" t="s">
-        <v>4287</v>
+      <c r="D536" s="3">
+        <v>5</v>
       </c>
       <c r="E536" s="3" t="s">
         <v>64</v>
@@ -42948,7 +42933,7 @@
         <v>4275</v>
       </c>
       <c r="D537" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E537" s="3" t="s">
         <v>215</v>
@@ -43002,7 +42987,7 @@
         <v>4274</v>
       </c>
       <c r="D538" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E538" s="3" t="s">
         <v>252</v>
@@ -43056,7 +43041,7 @@
         <v>4274</v>
       </c>
       <c r="D539" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E539" s="3" t="s">
         <v>242</v>
@@ -43106,7 +43091,7 @@
         <v>4274</v>
       </c>
       <c r="D540" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E540" s="3" t="s">
         <v>242</v>
@@ -43154,7 +43139,7 @@
         <v>4275</v>
       </c>
       <c r="D541" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E541" s="3" t="s">
         <v>242</v>
@@ -43208,7 +43193,7 @@
         <v>4273</v>
       </c>
       <c r="D542" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E542" s="3" t="s">
         <v>96</v>
@@ -43261,8 +43246,8 @@
       <c r="C543" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D543" s="3" t="s">
-        <v>4293</v>
+      <c r="D543" s="3">
+        <v>6</v>
       </c>
       <c r="E543" s="3" t="s">
         <v>122</v>
@@ -43313,8 +43298,8 @@
       <c r="C544" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D544" s="3" t="s">
-        <v>4287</v>
+      <c r="D544" s="3">
+        <v>5</v>
       </c>
       <c r="E544" s="3" t="s">
         <v>64</v>
@@ -43363,8 +43348,8 @@
       <c r="C545" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D545" s="3" t="s">
-        <v>4287</v>
+      <c r="D545" s="3">
+        <v>5</v>
       </c>
       <c r="E545" s="3" t="s">
         <v>64</v>
@@ -43414,7 +43399,7 @@
         <v>4273</v>
       </c>
       <c r="D546" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E546" s="3" t="s">
         <v>326</v>
@@ -43468,7 +43453,7 @@
         <v>4273</v>
       </c>
       <c r="D547" s="3" t="s">
-        <v>4314</v>
+        <v>4308</v>
       </c>
       <c r="E547" s="3" t="s">
         <v>1037</v>
@@ -43521,8 +43506,8 @@
       <c r="C548" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D548" s="3" t="s">
-        <v>4285</v>
+      <c r="D548" s="3">
+        <v>4</v>
       </c>
       <c r="E548" s="3" t="s">
         <v>40</v>
@@ -43575,8 +43560,8 @@
       <c r="C549" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D549" s="3" t="s">
-        <v>4287</v>
+      <c r="D549" s="3">
+        <v>5</v>
       </c>
       <c r="E549" s="3" t="s">
         <v>64</v>
@@ -43630,7 +43615,7 @@
         <v>4274</v>
       </c>
       <c r="D550" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E550" s="3" t="s">
         <v>96</v>
@@ -43684,7 +43669,7 @@
         <v>4273</v>
       </c>
       <c r="D551" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E551" s="3" t="s">
         <v>215</v>
@@ -43791,8 +43776,8 @@
       <c r="C553" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D553" s="3" t="s">
-        <v>4285</v>
+      <c r="D553" s="3">
+        <v>4</v>
       </c>
       <c r="E553" s="3" t="s">
         <v>40</v>
@@ -43846,7 +43831,7 @@
         <v>4274</v>
       </c>
       <c r="D554" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E554" s="3" t="s">
         <v>96</v>
@@ -43899,8 +43884,8 @@
       <c r="C555" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D555" s="3" t="s">
-        <v>4293</v>
+      <c r="D555" s="3">
+        <v>6</v>
       </c>
       <c r="E555" s="3" t="s">
         <v>122</v>
@@ -44008,7 +43993,7 @@
         <v>4273</v>
       </c>
       <c r="D557" s="3" t="s">
-        <v>4317</v>
+        <v>4311</v>
       </c>
       <c r="E557" s="3" t="s">
         <v>1352</v>
@@ -44062,7 +44047,7 @@
         <v>4274</v>
       </c>
       <c r="D558" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E558" s="3" t="s">
         <v>293</v>
@@ -44115,8 +44100,8 @@
       <c r="C559" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D559" s="3" t="s">
-        <v>4293</v>
+      <c r="D559" s="3">
+        <v>6</v>
       </c>
       <c r="E559" s="3" t="s">
         <v>122</v>
@@ -44170,7 +44155,7 @@
         <v>4274</v>
       </c>
       <c r="D560" s="3" t="s">
-        <v>4314</v>
+        <v>4308</v>
       </c>
       <c r="E560" s="3" t="s">
         <v>1037</v>
@@ -44498,7 +44483,7 @@
         <v>4274</v>
       </c>
       <c r="D567" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E567" s="3" t="s">
         <v>118</v>
@@ -44551,8 +44536,8 @@
       <c r="C568" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D568" s="3" t="s">
-        <v>4293</v>
+      <c r="D568" s="3">
+        <v>6</v>
       </c>
       <c r="E568" s="3" t="s">
         <v>122</v>
@@ -44601,8 +44586,8 @@
       <c r="C569" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D569" s="3" t="s">
-        <v>4293</v>
+      <c r="D569" s="3">
+        <v>6</v>
       </c>
       <c r="E569" s="3" t="s">
         <v>122</v>
@@ -44652,7 +44637,7 @@
         <v>4275</v>
       </c>
       <c r="D570" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E570" s="3" t="s">
         <v>215</v>
@@ -44702,7 +44687,7 @@
         <v>4273</v>
       </c>
       <c r="D571" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E571" s="3" t="s">
         <v>293</v>
@@ -44752,7 +44737,7 @@
         <v>4274</v>
       </c>
       <c r="D572" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E572" s="3" t="s">
         <v>494</v>
@@ -44801,8 +44786,8 @@
       <c r="C573" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D573" s="3" t="s">
-        <v>4289</v>
+      <c r="D573" s="3">
+        <v>9</v>
       </c>
       <c r="E573" s="3" t="s">
         <v>86</v>
@@ -44851,8 +44836,8 @@
       <c r="C574" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D574" s="3" t="s">
-        <v>4293</v>
+      <c r="D574" s="3">
+        <v>6</v>
       </c>
       <c r="E574" s="3" t="s">
         <v>122</v>
@@ -44902,7 +44887,7 @@
         <v>4274</v>
       </c>
       <c r="D575" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E575" s="3" t="s">
         <v>252</v>
@@ -44950,7 +44935,7 @@
         <v>4275</v>
       </c>
       <c r="D576" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E576" s="3" t="s">
         <v>215</v>
@@ -45108,7 +45093,7 @@
         <v>4274</v>
       </c>
       <c r="D579" s="3" t="s">
-        <v>4314</v>
+        <v>4308</v>
       </c>
       <c r="E579" s="3" t="s">
         <v>1037</v>
@@ -45161,8 +45146,8 @@
       <c r="C580" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D580" s="3" t="s">
-        <v>4284</v>
+      <c r="D580" s="3">
+        <v>7</v>
       </c>
       <c r="E580" s="3" t="s">
         <v>33</v>
@@ -45216,7 +45201,7 @@
         <v>4273</v>
       </c>
       <c r="D581" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E581" s="3" t="s">
         <v>326</v>
@@ -45270,7 +45255,7 @@
         <v>4274</v>
       </c>
       <c r="D582" s="3" t="s">
-        <v>4314</v>
+        <v>4308</v>
       </c>
       <c r="E582" s="3" t="s">
         <v>1037</v>
@@ -45323,8 +45308,8 @@
       <c r="C583" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D583" s="3" t="s">
-        <v>4284</v>
+      <c r="D583" s="3">
+        <v>7</v>
       </c>
       <c r="E583" s="3" t="s">
         <v>33</v>
@@ -45378,7 +45363,7 @@
         <v>4275</v>
       </c>
       <c r="D584" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E584" s="3" t="s">
         <v>96</v>
@@ -45432,7 +45417,7 @@
         <v>4273</v>
       </c>
       <c r="D585" s="3" t="s">
-        <v>4318</v>
+        <v>4312</v>
       </c>
       <c r="E585" s="3" t="s">
         <v>1566</v>
@@ -45482,7 +45467,7 @@
         <v>4275</v>
       </c>
       <c r="D586" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E586" s="3" t="s">
         <v>215</v>
@@ -45535,8 +45520,8 @@
       <c r="C587" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D587" s="3" t="s">
-        <v>4293</v>
+      <c r="D587" s="3">
+        <v>6</v>
       </c>
       <c r="E587" s="3" t="s">
         <v>122</v>
@@ -45589,8 +45574,8 @@
       <c r="C588" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D588" s="3" t="s">
-        <v>4287</v>
+      <c r="D588" s="3">
+        <v>5</v>
       </c>
       <c r="E588" s="3" t="s">
         <v>64</v>
@@ -45643,8 +45628,8 @@
       <c r="C589" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D589" s="3" t="s">
-        <v>4284</v>
+      <c r="D589" s="3">
+        <v>7</v>
       </c>
       <c r="E589" s="3" t="s">
         <v>33</v>
@@ -45793,8 +45778,8 @@
       <c r="C592" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D592" s="3" t="s">
-        <v>4287</v>
+      <c r="D592" s="3">
+        <v>5</v>
       </c>
       <c r="E592" s="3" t="s">
         <v>64</v>
@@ -45844,7 +45829,7 @@
         <v>4274</v>
       </c>
       <c r="D593" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E593" s="3" t="s">
         <v>215</v>
@@ -45893,8 +45878,8 @@
       <c r="C594" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D594" s="3" t="s">
-        <v>4284</v>
+      <c r="D594" s="3">
+        <v>7</v>
       </c>
       <c r="E594" s="3" t="s">
         <v>33</v>
@@ -45947,8 +45932,8 @@
       <c r="C595" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D595" s="3" t="s">
-        <v>4284</v>
+      <c r="D595" s="3">
+        <v>7</v>
       </c>
       <c r="E595" s="3" t="s">
         <v>302</v>
@@ -45996,7 +45981,7 @@
         <v>4274</v>
       </c>
       <c r="D596" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E596" s="3" t="s">
         <v>498</v>
@@ -46050,7 +46035,7 @@
         <v>4273</v>
       </c>
       <c r="D597" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E597" s="3" t="s">
         <v>118</v>
@@ -48136,7 +48121,7 @@
         <v>4274</v>
       </c>
       <c r="D638" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E638" s="3" t="s">
         <v>333</v>
@@ -48190,7 +48175,7 @@
         <v>4274</v>
       </c>
       <c r="D639" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E639" s="3" t="s">
         <v>96</v>
@@ -48243,8 +48228,8 @@
       <c r="C640" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D640" s="3" t="s">
-        <v>4287</v>
+      <c r="D640" s="3">
+        <v>5</v>
       </c>
       <c r="E640" s="3" t="s">
         <v>64</v>
@@ -48298,7 +48283,7 @@
         <v>4273</v>
       </c>
       <c r="D641" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E641" s="3" t="s">
         <v>498</v>
@@ -48351,8 +48336,8 @@
       <c r="C642" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D642" s="3" t="s">
-        <v>4293</v>
+      <c r="D642" s="3">
+        <v>6</v>
       </c>
       <c r="E642" s="3" t="s">
         <v>896</v>
@@ -48404,7 +48389,7 @@
         <v>4273</v>
       </c>
       <c r="D643" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E643" s="3" t="s">
         <v>227</v>
@@ -48457,8 +48442,8 @@
       <c r="C644" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D644" s="3" t="s">
-        <v>4293</v>
+      <c r="D644" s="3">
+        <v>6</v>
       </c>
       <c r="E644" s="3" t="s">
         <v>122</v>
@@ -48510,7 +48495,7 @@
         <v>4274</v>
       </c>
       <c r="D645" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E645" s="3" t="s">
         <v>118</v>
@@ -48564,7 +48549,7 @@
         <v>4273</v>
       </c>
       <c r="D646" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E646" s="3" t="s">
         <v>326</v>
@@ -48618,7 +48603,7 @@
         <v>4273</v>
       </c>
       <c r="D647" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E647" s="3" t="s">
         <v>498</v>
@@ -48771,8 +48756,8 @@
       <c r="C650" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D650" s="3" t="s">
-        <v>4293</v>
+      <c r="D650" s="3">
+        <v>6</v>
       </c>
       <c r="E650" s="3" t="s">
         <v>122</v>
@@ -48826,7 +48811,7 @@
         <v>4274</v>
       </c>
       <c r="D651" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E651" s="3" t="s">
         <v>130</v>
@@ -48879,8 +48864,8 @@
       <c r="C652" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D652" s="3" t="s">
-        <v>4293</v>
+      <c r="D652" s="3">
+        <v>6</v>
       </c>
       <c r="E652" s="3" t="s">
         <v>122</v>
@@ -48929,8 +48914,8 @@
       <c r="C653" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D653" s="3" t="s">
-        <v>4289</v>
+      <c r="D653" s="3">
+        <v>9</v>
       </c>
       <c r="E653" s="3" t="s">
         <v>86</v>
@@ -49037,8 +49022,8 @@
       <c r="C655" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D655" s="3" t="s">
-        <v>4285</v>
+      <c r="D655" s="3">
+        <v>4</v>
       </c>
       <c r="E655" s="3" t="s">
         <v>40</v>
@@ -49089,8 +49074,8 @@
       <c r="C656" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D656" s="3" t="s">
-        <v>4284</v>
+      <c r="D656" s="3">
+        <v>7</v>
       </c>
       <c r="E656" s="3" t="s">
         <v>33</v>
@@ -49187,8 +49172,8 @@
       <c r="C658" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D658" s="3" t="s">
-        <v>4289</v>
+      <c r="D658" s="3">
+        <v>9</v>
       </c>
       <c r="E658" s="3" t="s">
         <v>86</v>
@@ -49239,8 +49224,8 @@
       <c r="C659" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D659" s="3" t="s">
-        <v>4293</v>
+      <c r="D659" s="3">
+        <v>6</v>
       </c>
       <c r="E659" s="3" t="s">
         <v>122</v>
@@ -49293,8 +49278,8 @@
       <c r="C660" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D660" s="3" t="s">
-        <v>4287</v>
+      <c r="D660" s="3">
+        <v>5</v>
       </c>
       <c r="E660" s="3" t="s">
         <v>64</v>
@@ -49344,7 +49329,7 @@
         <v>4273</v>
       </c>
       <c r="D661" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E661" s="3" t="s">
         <v>118</v>
@@ -49394,7 +49379,7 @@
         <v>4274</v>
       </c>
       <c r="D662" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E662" s="3" t="s">
         <v>215</v>
@@ -49444,7 +49429,7 @@
         <v>4274</v>
       </c>
       <c r="D663" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E663" s="3" t="s">
         <v>222</v>
@@ -49498,7 +49483,7 @@
         <v>4273</v>
       </c>
       <c r="D664" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E664" s="3" t="s">
         <v>215</v>
@@ -49551,8 +49536,8 @@
       <c r="C665" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D665" s="3" t="s">
-        <v>4285</v>
+      <c r="D665" s="3">
+        <v>4</v>
       </c>
       <c r="E665" s="3" t="s">
         <v>40</v>
@@ -49606,7 +49591,7 @@
         <v>4273</v>
       </c>
       <c r="D666" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E666" s="3" t="s">
         <v>326</v>
@@ -49708,7 +49693,7 @@
         <v>4274</v>
       </c>
       <c r="D668" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E668" s="3" t="s">
         <v>227</v>
@@ -49761,8 +49746,8 @@
       <c r="C669" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D669" s="3" t="s">
-        <v>4287</v>
+      <c r="D669" s="3">
+        <v>5</v>
       </c>
       <c r="E669" s="3" t="s">
         <v>64</v>
@@ -50766,7 +50751,7 @@
         <v>4274</v>
       </c>
       <c r="D689" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E689" s="3" t="s">
         <v>96</v>
@@ -50819,8 +50804,8 @@
       <c r="C690" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D690" s="3" t="s">
-        <v>4287</v>
+      <c r="D690" s="3">
+        <v>5</v>
       </c>
       <c r="E690" s="3" t="s">
         <v>64</v>
@@ -50873,8 +50858,8 @@
       <c r="C691" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D691" s="3" t="s">
-        <v>4293</v>
+      <c r="D691" s="3">
+        <v>6</v>
       </c>
       <c r="E691" s="3" t="s">
         <v>122</v>
@@ -50928,7 +50913,7 @@
         <v>4274</v>
       </c>
       <c r="D692" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E692" s="3" t="s">
         <v>227</v>
@@ -50978,7 +50963,7 @@
         <v>4273</v>
       </c>
       <c r="D693" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E693" s="3" t="s">
         <v>494</v>
@@ -51027,8 +51012,8 @@
       <c r="C694" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D694" s="3" t="s">
-        <v>4293</v>
+      <c r="D694" s="3">
+        <v>6</v>
       </c>
       <c r="E694" s="3" t="s">
         <v>122</v>
@@ -51079,8 +51064,8 @@
       <c r="C695" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D695" s="3" t="s">
-        <v>4293</v>
+      <c r="D695" s="3">
+        <v>6</v>
       </c>
       <c r="E695" s="3" t="s">
         <v>122</v>
@@ -51134,7 +51119,7 @@
         <v>4273</v>
       </c>
       <c r="D696" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E696" s="3" t="s">
         <v>498</v>
@@ -51237,8 +51222,8 @@
       <c r="C698" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D698" s="3" t="s">
-        <v>4287</v>
+      <c r="D698" s="3">
+        <v>5</v>
       </c>
       <c r="E698" s="3" t="s">
         <v>64</v>
@@ -51289,8 +51274,8 @@
       <c r="C699" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D699" s="3" t="s">
-        <v>4287</v>
+      <c r="D699" s="3">
+        <v>5</v>
       </c>
       <c r="E699" s="3" t="s">
         <v>64</v>
@@ -51442,7 +51427,7 @@
         <v>4275</v>
       </c>
       <c r="D702" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E702" s="3" t="s">
         <v>215</v>
@@ -52132,7 +52117,7 @@
         <v>4275</v>
       </c>
       <c r="D716" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E716" s="3" t="s">
         <v>333</v>
@@ -52186,7 +52171,7 @@
         <v>4275</v>
       </c>
       <c r="D717" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E717" s="3" t="s">
         <v>96</v>
@@ -52239,8 +52224,8 @@
       <c r="C718" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D718" s="3" t="s">
-        <v>4289</v>
+      <c r="D718" s="3">
+        <v>9</v>
       </c>
       <c r="E718" s="3" t="s">
         <v>86</v>
@@ -52294,7 +52279,7 @@
         <v>4274</v>
       </c>
       <c r="D719" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E719" s="3" t="s">
         <v>252</v>
@@ -52348,7 +52333,7 @@
         <v>4273</v>
       </c>
       <c r="D720" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E720" s="3" t="s">
         <v>326</v>
@@ -52751,8 +52736,8 @@
       <c r="C728" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D728" s="3" t="s">
-        <v>4284</v>
+      <c r="D728" s="3">
+        <v>7</v>
       </c>
       <c r="E728" s="3" t="s">
         <v>33</v>
@@ -52803,8 +52788,8 @@
       <c r="C729" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D729" s="3" t="s">
-        <v>4293</v>
+      <c r="D729" s="3">
+        <v>6</v>
       </c>
       <c r="E729" s="3" t="s">
         <v>122</v>
@@ -52853,8 +52838,8 @@
       <c r="C730" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D730" s="3" t="s">
-        <v>4293</v>
+      <c r="D730" s="3">
+        <v>6</v>
       </c>
       <c r="E730" s="3" t="s">
         <v>122</v>
@@ -53211,8 +53196,8 @@
       <c r="C737" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D737" s="3" t="s">
-        <v>4284</v>
+      <c r="D737" s="3">
+        <v>7</v>
       </c>
       <c r="E737" s="3" t="s">
         <v>33</v>
@@ -53263,8 +53248,8 @@
       <c r="C738" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D738" s="3" t="s">
-        <v>4284</v>
+      <c r="D738" s="3">
+        <v>7</v>
       </c>
       <c r="E738" s="3" t="s">
         <v>33</v>
@@ -53315,8 +53300,8 @@
       <c r="C739" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D739" s="3" t="s">
-        <v>4284</v>
+      <c r="D739" s="3">
+        <v>7</v>
       </c>
       <c r="E739" s="3" t="s">
         <v>33</v>
@@ -53367,8 +53352,8 @@
       <c r="C740" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D740" s="3" t="s">
-        <v>4284</v>
+      <c r="D740" s="3">
+        <v>7</v>
       </c>
       <c r="E740" s="3" t="s">
         <v>33</v>
@@ -53419,8 +53404,8 @@
       <c r="C741" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D741" s="3" t="s">
-        <v>4284</v>
+      <c r="D741" s="3">
+        <v>7</v>
       </c>
       <c r="E741" s="3" t="s">
         <v>33</v>
@@ -53471,8 +53456,8 @@
       <c r="C742" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D742" s="3" t="s">
-        <v>4284</v>
+      <c r="D742" s="3">
+        <v>7</v>
       </c>
       <c r="E742" s="3" t="s">
         <v>33</v>
@@ -53523,8 +53508,8 @@
       <c r="C743" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D743" s="3" t="s">
-        <v>4284</v>
+      <c r="D743" s="3">
+        <v>7</v>
       </c>
       <c r="E743" s="3" t="s">
         <v>33</v>
@@ -53575,8 +53560,8 @@
       <c r="C744" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D744" s="3" t="s">
-        <v>4284</v>
+      <c r="D744" s="3">
+        <v>7</v>
       </c>
       <c r="E744" s="3" t="s">
         <v>33</v>
@@ -53623,8 +53608,8 @@
       <c r="C745" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D745" s="3" t="s">
-        <v>4284</v>
+      <c r="D745" s="3">
+        <v>7</v>
       </c>
       <c r="E745" s="3" t="s">
         <v>33</v>
@@ -53675,8 +53660,8 @@
       <c r="C746" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D746" s="3" t="s">
-        <v>4284</v>
+      <c r="D746" s="3">
+        <v>7</v>
       </c>
       <c r="E746" s="3" t="s">
         <v>33</v>
@@ -53727,8 +53712,8 @@
       <c r="C747" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D747" s="3" t="s">
-        <v>4284</v>
+      <c r="D747" s="3">
+        <v>7</v>
       </c>
       <c r="E747" s="3" t="s">
         <v>33</v>
@@ -53779,8 +53764,8 @@
       <c r="C748" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D748" s="3" t="s">
-        <v>4284</v>
+      <c r="D748" s="3">
+        <v>7</v>
       </c>
       <c r="E748" s="3" t="s">
         <v>33</v>
@@ -53832,7 +53817,7 @@
         <v>4275</v>
       </c>
       <c r="D749" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E749" s="3" t="s">
         <v>498</v>
@@ -53886,7 +53871,7 @@
         <v>4274</v>
       </c>
       <c r="D750" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E750" s="3" t="s">
         <v>498</v>
@@ -53940,7 +53925,7 @@
         <v>4275</v>
       </c>
       <c r="D751" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E751" s="3" t="s">
         <v>227</v>
@@ -53992,7 +53977,7 @@
         <v>4274</v>
       </c>
       <c r="D752" s="3" t="s">
-        <v>4322</v>
+        <v>4316</v>
       </c>
       <c r="E752" s="3" t="s">
         <v>2523</v>
@@ -54041,8 +54026,8 @@
       <c r="C753" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D753" s="3" t="s">
-        <v>4287</v>
+      <c r="D753" s="3">
+        <v>5</v>
       </c>
       <c r="E753" s="3" t="s">
         <v>64</v>
@@ -54092,7 +54077,7 @@
         <v>4273</v>
       </c>
       <c r="D754" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E754" s="3" t="s">
         <v>130</v>
@@ -54141,8 +54126,8 @@
       <c r="C755" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D755" s="3" t="s">
-        <v>4284</v>
+      <c r="D755" s="3">
+        <v>7</v>
       </c>
       <c r="E755" s="3" t="s">
         <v>33</v>
@@ -54192,7 +54177,7 @@
         <v>4275</v>
       </c>
       <c r="D756" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E756" s="3" t="s">
         <v>215</v>
@@ -54293,8 +54278,8 @@
       <c r="C758" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D758" s="3" t="s">
-        <v>4284</v>
+      <c r="D758" s="3">
+        <v>7</v>
       </c>
       <c r="E758" s="3" t="s">
         <v>302</v>
@@ -54345,8 +54330,8 @@
       <c r="C759" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D759" s="3" t="s">
-        <v>4284</v>
+      <c r="D759" s="3">
+        <v>7</v>
       </c>
       <c r="E759" s="3" t="s">
         <v>302</v>
@@ -54398,7 +54383,7 @@
         <v>4274</v>
       </c>
       <c r="D760" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E760" s="3" t="s">
         <v>333</v>
@@ -54447,8 +54432,8 @@
       <c r="C761" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D761" s="3" t="s">
-        <v>4289</v>
+      <c r="D761" s="3">
+        <v>9</v>
       </c>
       <c r="E761" s="3" t="s">
         <v>86</v>
@@ -54498,7 +54483,7 @@
         <v>4273</v>
       </c>
       <c r="D762" s="3" t="s">
-        <v>4312</v>
+        <v>4306</v>
       </c>
       <c r="E762" s="3" t="s">
         <v>749</v>
@@ -54548,7 +54533,7 @@
         <v>4275</v>
       </c>
       <c r="D763" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E763" s="3" t="s">
         <v>215</v>
@@ -54601,8 +54586,8 @@
       <c r="C764" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D764" s="3" t="s">
-        <v>4286</v>
+      <c r="D764" s="3">
+        <v>8</v>
       </c>
       <c r="E764" s="3" t="s">
         <v>57</v>
@@ -54651,8 +54636,8 @@
       <c r="C765" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D765" s="3" t="s">
-        <v>4293</v>
+      <c r="D765" s="3">
+        <v>6</v>
       </c>
       <c r="E765" s="3" t="s">
         <v>122</v>
@@ -54699,8 +54684,8 @@
       <c r="C766" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D766" s="3" t="s">
-        <v>4284</v>
+      <c r="D766" s="3">
+        <v>7</v>
       </c>
       <c r="E766" s="3" t="s">
         <v>33</v>
@@ -54754,7 +54739,7 @@
         <v>4273</v>
       </c>
       <c r="D767" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E767" s="3" t="s">
         <v>215</v>
@@ -54808,7 +54793,7 @@
         <v>4276</v>
       </c>
       <c r="D768" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E768" s="3" t="s">
         <v>498</v>
@@ -54862,7 +54847,7 @@
         <v>4275</v>
       </c>
       <c r="D769" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E769" s="3" t="s">
         <v>215</v>
@@ -54916,7 +54901,7 @@
         <v>4274</v>
       </c>
       <c r="D770" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E770" s="3" t="s">
         <v>96</v>
@@ -54970,7 +54955,7 @@
         <v>4274</v>
       </c>
       <c r="D771" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E771" s="3" t="s">
         <v>333</v>
@@ -55023,8 +55008,8 @@
       <c r="C772" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D772" s="3" t="s">
-        <v>4293</v>
+      <c r="D772" s="3">
+        <v>6</v>
       </c>
       <c r="E772" s="3" t="s">
         <v>122</v>
@@ -55078,7 +55063,7 @@
         <v>4274</v>
       </c>
       <c r="D773" s="3" t="s">
-        <v>4296</v>
+        <v>4290</v>
       </c>
       <c r="E773" s="3" t="s">
         <v>188</v>
@@ -55131,8 +55116,8 @@
       <c r="C774" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D774" s="3" t="s">
-        <v>4293</v>
+      <c r="D774" s="3">
+        <v>6</v>
       </c>
       <c r="E774" s="3" t="s">
         <v>896</v>
@@ -55186,7 +55171,7 @@
         <v>4274</v>
       </c>
       <c r="D775" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E775" s="3" t="s">
         <v>227</v>
@@ -55240,7 +55225,7 @@
         <v>4274</v>
       </c>
       <c r="D776" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E776" s="3" t="s">
         <v>498</v>
@@ -55293,8 +55278,8 @@
       <c r="C777" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D777" s="3" t="s">
-        <v>4293</v>
+      <c r="D777" s="3">
+        <v>6</v>
       </c>
       <c r="E777" s="3" t="s">
         <v>122</v>
@@ -55348,7 +55333,7 @@
         <v>4274</v>
       </c>
       <c r="D778" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E778" s="3" t="s">
         <v>498</v>
@@ -55401,8 +55386,8 @@
       <c r="C779" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D779" s="3" t="s">
-        <v>4293</v>
+      <c r="D779" s="3">
+        <v>6</v>
       </c>
       <c r="E779" s="3" t="s">
         <v>122</v>
@@ -55456,7 +55441,7 @@
         <v>4274</v>
       </c>
       <c r="D780" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E780" s="3" t="s">
         <v>215</v>
@@ -55564,7 +55549,7 @@
         <v>4273</v>
       </c>
       <c r="D782" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E782" s="3" t="s">
         <v>252</v>
@@ -55617,8 +55602,8 @@
       <c r="C783" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D783" s="3" t="s">
-        <v>4284</v>
+      <c r="D783" s="3">
+        <v>7</v>
       </c>
       <c r="E783" s="3" t="s">
         <v>33</v>
@@ -55670,7 +55655,7 @@
         <v>4275</v>
       </c>
       <c r="D784" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E784" s="3" t="s">
         <v>215</v>
@@ -55724,7 +55709,7 @@
         <v>4275</v>
       </c>
       <c r="D785" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E785" s="3" t="s">
         <v>242</v>
@@ -55778,7 +55763,7 @@
         <v>4274</v>
       </c>
       <c r="D786" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E786" s="3" t="s">
         <v>96</v>
@@ -55832,7 +55817,7 @@
         <v>4274</v>
       </c>
       <c r="D787" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E787" s="3" t="s">
         <v>130</v>
@@ -55882,7 +55867,7 @@
         <v>4274</v>
       </c>
       <c r="D788" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E788" s="3" t="s">
         <v>326</v>
@@ -55936,7 +55921,7 @@
         <v>4274</v>
       </c>
       <c r="D789" s="3" t="s">
-        <v>4323</v>
+        <v>4317</v>
       </c>
       <c r="E789" s="3" t="s">
         <v>2617</v>
@@ -55990,7 +55975,7 @@
         <v>4274</v>
       </c>
       <c r="D790" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E790" s="3" t="s">
         <v>566</v>
@@ -56043,8 +56028,8 @@
       <c r="C791" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D791" s="3" t="s">
-        <v>4286</v>
+      <c r="D791" s="3">
+        <v>8</v>
       </c>
       <c r="E791" s="3" t="s">
         <v>57</v>
@@ -56098,7 +56083,7 @@
         <v>4274</v>
       </c>
       <c r="D792" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E792" s="3" t="s">
         <v>227</v>
@@ -56152,7 +56137,7 @@
         <v>4274</v>
       </c>
       <c r="D793" s="3" t="s">
-        <v>4317</v>
+        <v>4311</v>
       </c>
       <c r="E793" s="3" t="s">
         <v>1352</v>
@@ -56206,7 +56191,7 @@
         <v>4274</v>
       </c>
       <c r="D794" s="3" t="s">
-        <v>4314</v>
+        <v>4308</v>
       </c>
       <c r="E794" s="3" t="s">
         <v>1037</v>
@@ -56260,7 +56245,7 @@
         <v>4274</v>
       </c>
       <c r="D795" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E795" s="3" t="s">
         <v>293</v>
@@ -56314,7 +56299,7 @@
         <v>4274</v>
       </c>
       <c r="D796" s="3" t="s">
-        <v>4312</v>
+        <v>4306</v>
       </c>
       <c r="E796" s="3" t="s">
         <v>749</v>
@@ -56368,7 +56353,7 @@
         <v>4274</v>
       </c>
       <c r="D797" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E797" s="3" t="s">
         <v>333</v>
@@ -56422,7 +56407,7 @@
         <v>4274</v>
       </c>
       <c r="D798" s="3" t="s">
-        <v>4319</v>
+        <v>4313</v>
       </c>
       <c r="E798" s="3" t="s">
         <v>1643</v>
@@ -56476,7 +56461,7 @@
         <v>4274</v>
       </c>
       <c r="D799" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E799" s="3" t="s">
         <v>498</v>
@@ -56526,7 +56511,7 @@
         <v>4273</v>
       </c>
       <c r="D800" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E800" s="3" t="s">
         <v>498</v>
@@ -56580,7 +56565,7 @@
         <v>4273</v>
       </c>
       <c r="D801" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E801" s="3" t="s">
         <v>498</v>
@@ -56634,7 +56619,7 @@
         <v>4273</v>
       </c>
       <c r="D802" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E802" s="3" t="s">
         <v>118</v>
@@ -56688,7 +56673,7 @@
         <v>4274</v>
       </c>
       <c r="D803" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E803" s="3" t="s">
         <v>252</v>
@@ -56741,8 +56726,8 @@
       <c r="C804" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D804" s="3" t="s">
-        <v>4293</v>
+      <c r="D804" s="3">
+        <v>6</v>
       </c>
       <c r="E804" s="3" t="s">
         <v>122</v>
@@ -56795,8 +56780,8 @@
       <c r="C805" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D805" s="3" t="s">
-        <v>4293</v>
+      <c r="D805" s="3">
+        <v>6</v>
       </c>
       <c r="E805" s="3" t="s">
         <v>122</v>
@@ -56845,8 +56830,8 @@
       <c r="C806" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D806" s="3" t="s">
-        <v>4287</v>
+      <c r="D806" s="3">
+        <v>5</v>
       </c>
       <c r="E806" s="3" t="s">
         <v>64</v>
@@ -56895,8 +56880,8 @@
       <c r="C807" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D807" s="3" t="s">
-        <v>4284</v>
+      <c r="D807" s="3">
+        <v>7</v>
       </c>
       <c r="E807" s="3" t="s">
         <v>33</v>
@@ -57210,7 +57195,7 @@
         <v>4274</v>
       </c>
       <c r="D813" s="3" t="s">
-        <v>4324</v>
+        <v>4318</v>
       </c>
       <c r="E813" s="3" t="s">
         <v>2669</v>
@@ -57264,7 +57249,7 @@
         <v>4274</v>
       </c>
       <c r="D814" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E814" s="3" t="s">
         <v>215</v>
@@ -57316,7 +57301,7 @@
         <v>4274</v>
       </c>
       <c r="D815" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E815" s="3" t="s">
         <v>227</v>
@@ -57369,8 +57354,8 @@
       <c r="C816" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D816" s="3" t="s">
-        <v>4287</v>
+      <c r="D816" s="3">
+        <v>5</v>
       </c>
       <c r="E816" s="3" t="s">
         <v>64</v>
@@ -57421,8 +57406,8 @@
       <c r="C817" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D817" s="3" t="s">
-        <v>4284</v>
+      <c r="D817" s="3">
+        <v>7</v>
       </c>
       <c r="E817" s="3" t="s">
         <v>33</v>
@@ -57469,8 +57454,8 @@
       <c r="C818" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D818" s="3" t="s">
-        <v>4284</v>
+      <c r="D818" s="3">
+        <v>7</v>
       </c>
       <c r="E818" s="3" t="s">
         <v>302</v>
@@ -57520,7 +57505,7 @@
         <v>4274</v>
       </c>
       <c r="D819" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E819" s="3" t="s">
         <v>227</v>
@@ -57627,8 +57612,8 @@
       <c r="C821" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D821" s="3" t="s">
-        <v>4289</v>
+      <c r="D821" s="3">
+        <v>9</v>
       </c>
       <c r="E821" s="3" t="s">
         <v>86</v>
@@ -57682,7 +57667,7 @@
         <v>4274</v>
       </c>
       <c r="D822" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E822" s="3" t="s">
         <v>222</v>
@@ -57736,7 +57721,7 @@
         <v>4273</v>
       </c>
       <c r="D823" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E823" s="3" t="s">
         <v>222</v>
@@ -57790,7 +57775,7 @@
         <v>4275</v>
       </c>
       <c r="D824" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E824" s="3" t="s">
         <v>227</v>
@@ -57839,8 +57824,8 @@
       <c r="C825" s="3" t="s">
         <v>4271</v>
       </c>
-      <c r="D825" s="3" t="s">
-        <v>4284</v>
+      <c r="D825" s="3">
+        <v>7</v>
       </c>
       <c r="E825" s="3" t="s">
         <v>33</v>
@@ -57889,8 +57874,8 @@
       <c r="C826" s="3" t="s">
         <v>4271</v>
       </c>
-      <c r="D826" s="3" t="s">
-        <v>4284</v>
+      <c r="D826" s="3">
+        <v>7</v>
       </c>
       <c r="E826" s="3" t="s">
         <v>33</v>
@@ -57941,8 +57926,8 @@
       <c r="C827" s="3" t="s">
         <v>4271</v>
       </c>
-      <c r="D827" s="3" t="s">
-        <v>4284</v>
+      <c r="D827" s="3">
+        <v>7</v>
       </c>
       <c r="E827" s="3" t="s">
         <v>33</v>
@@ -57994,7 +57979,7 @@
         <v>4274</v>
       </c>
       <c r="D828" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E828" s="3" t="s">
         <v>326</v>
@@ -58147,8 +58132,8 @@
       <c r="C831" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D831" s="3" t="s">
-        <v>4287</v>
+      <c r="D831" s="3">
+        <v>5</v>
       </c>
       <c r="E831" s="3" t="s">
         <v>64</v>
@@ -58256,7 +58241,7 @@
         <v>4274</v>
       </c>
       <c r="D833" s="3" t="s">
-        <v>4313</v>
+        <v>4307</v>
       </c>
       <c r="E833" s="3" t="s">
         <v>844</v>
@@ -58309,8 +58294,8 @@
       <c r="C834" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D834" s="3" t="s">
-        <v>4287</v>
+      <c r="D834" s="3">
+        <v>5</v>
       </c>
       <c r="E834" s="3" t="s">
         <v>64</v>
@@ -58364,7 +58349,7 @@
         <v>4274</v>
       </c>
       <c r="D835" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E835" s="3" t="s">
         <v>293</v>
@@ -58417,8 +58402,8 @@
       <c r="C836" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D836" s="3" t="s">
-        <v>4284</v>
+      <c r="D836" s="3">
+        <v>7</v>
       </c>
       <c r="E836" s="3" t="s">
         <v>33</v>
@@ -58472,7 +58457,7 @@
         <v>4273</v>
       </c>
       <c r="D837" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E837" s="3" t="s">
         <v>130</v>
@@ -58525,8 +58510,8 @@
       <c r="C838" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D838" s="3" t="s">
-        <v>4284</v>
+      <c r="D838" s="3">
+        <v>7</v>
       </c>
       <c r="E838" s="3" t="s">
         <v>33</v>
@@ -58580,7 +58565,7 @@
         <v>4273</v>
       </c>
       <c r="D839" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E839" s="3" t="s">
         <v>494</v>
@@ -58629,8 +58614,8 @@
       <c r="C840" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D840" s="3" t="s">
-        <v>4286</v>
+      <c r="D840" s="3">
+        <v>8</v>
       </c>
       <c r="E840" s="3" t="s">
         <v>57</v>
@@ -58684,7 +58669,7 @@
         <v>4275</v>
       </c>
       <c r="D841" s="3" t="s">
-        <v>4296</v>
+        <v>4290</v>
       </c>
       <c r="E841" s="3" t="s">
         <v>188</v>
@@ -58738,7 +58723,7 @@
         <v>4274</v>
       </c>
       <c r="D842" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E842" s="3" t="s">
         <v>326</v>
@@ -58790,7 +58775,7 @@
         <v>4274</v>
       </c>
       <c r="D843" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E843" s="3" t="s">
         <v>498</v>
@@ -58844,7 +58829,7 @@
         <v>4274</v>
       </c>
       <c r="D844" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E844" s="3" t="s">
         <v>498</v>
@@ -58898,7 +58883,7 @@
         <v>4275</v>
       </c>
       <c r="D845" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E845" s="3" t="s">
         <v>215</v>
@@ -58999,8 +58984,8 @@
       <c r="C847" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D847" s="3" t="s">
-        <v>4293</v>
+      <c r="D847" s="3">
+        <v>6</v>
       </c>
       <c r="E847" s="3" t="s">
         <v>122</v>
@@ -59108,7 +59093,7 @@
         <v>4273</v>
       </c>
       <c r="D849" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E849" s="3" t="s">
         <v>498</v>
@@ -59161,8 +59146,8 @@
       <c r="C850" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D850" s="3" t="s">
-        <v>4293</v>
+      <c r="D850" s="3">
+        <v>6</v>
       </c>
       <c r="E850" s="3" t="s">
         <v>122</v>
@@ -59215,8 +59200,8 @@
       <c r="C851" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D851" s="3" t="s">
-        <v>4287</v>
+      <c r="D851" s="3">
+        <v>5</v>
       </c>
       <c r="E851" s="3" t="s">
         <v>64</v>
@@ -59270,7 +59255,7 @@
         <v>4273</v>
       </c>
       <c r="D852" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E852" s="3" t="s">
         <v>96</v>
@@ -59324,7 +59309,7 @@
         <v>4273</v>
       </c>
       <c r="D853" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E853" s="3" t="s">
         <v>263</v>
@@ -59431,8 +59416,8 @@
       <c r="C855" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D855" s="3" t="s">
-        <v>4287</v>
+      <c r="D855" s="3">
+        <v>5</v>
       </c>
       <c r="E855" s="3" t="s">
         <v>64</v>
@@ -59485,8 +59470,8 @@
       <c r="C856" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D856" s="3" t="s">
-        <v>4284</v>
+      <c r="D856" s="3">
+        <v>7</v>
       </c>
       <c r="E856" s="3" t="s">
         <v>33</v>
@@ -59539,8 +59524,8 @@
       <c r="C857" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D857" s="3" t="s">
-        <v>4287</v>
+      <c r="D857" s="3">
+        <v>5</v>
       </c>
       <c r="E857" s="3" t="s">
         <v>2797</v>
@@ -59591,8 +59576,8 @@
       <c r="C858" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D858" s="3" t="s">
-        <v>4287</v>
+      <c r="D858" s="3">
+        <v>5</v>
       </c>
       <c r="E858" s="3" t="s">
         <v>64</v>
@@ -59700,7 +59685,7 @@
         <v>4273</v>
       </c>
       <c r="D860" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E860" s="3" t="s">
         <v>326</v>
@@ -59754,7 +59739,7 @@
         <v>4275</v>
       </c>
       <c r="D861" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E861" s="3" t="s">
         <v>498</v>
@@ -59808,7 +59793,7 @@
         <v>4273</v>
       </c>
       <c r="D862" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E862" s="3" t="s">
         <v>252</v>
@@ -59966,7 +59951,7 @@
         <v>4274</v>
       </c>
       <c r="D865" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E865" s="3" t="s">
         <v>263</v>
@@ -60020,7 +60005,7 @@
         <v>4274</v>
       </c>
       <c r="D866" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E866" s="3" t="s">
         <v>118</v>
@@ -60072,7 +60057,7 @@
         <v>4274</v>
       </c>
       <c r="D867" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E867" s="3" t="s">
         <v>227</v>
@@ -60125,8 +60110,8 @@
       <c r="C868" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D868" s="3" t="s">
-        <v>4284</v>
+      <c r="D868" s="3">
+        <v>7</v>
       </c>
       <c r="E868" s="3" t="s">
         <v>33</v>
@@ -60180,7 +60165,7 @@
         <v>4276</v>
       </c>
       <c r="D869" s="3" t="s">
-        <v>4323</v>
+        <v>4317</v>
       </c>
       <c r="E869" s="3" t="s">
         <v>2617</v>
@@ -60234,7 +60219,7 @@
         <v>4275</v>
       </c>
       <c r="D870" s="3" t="s">
-        <v>4313</v>
+        <v>4307</v>
       </c>
       <c r="E870" s="3" t="s">
         <v>844</v>
@@ -60342,7 +60327,7 @@
         <v>4274</v>
       </c>
       <c r="D872" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E872" s="3" t="s">
         <v>252</v>
@@ -60391,8 +60376,8 @@
       <c r="C873" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D873" s="3" t="s">
-        <v>4284</v>
+      <c r="D873" s="3">
+        <v>7</v>
       </c>
       <c r="E873" s="3" t="s">
         <v>33</v>
@@ -60445,8 +60430,8 @@
       <c r="C874" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D874" s="3" t="s">
-        <v>4284</v>
+      <c r="D874" s="3">
+        <v>7</v>
       </c>
       <c r="E874" s="3" t="s">
         <v>33</v>
@@ -60497,8 +60482,8 @@
       <c r="C875" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D875" s="3" t="s">
-        <v>4284</v>
+      <c r="D875" s="3">
+        <v>7</v>
       </c>
       <c r="E875" s="3" t="s">
         <v>33</v>
@@ -60549,8 +60534,8 @@
       <c r="C876" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D876" s="3" t="s">
-        <v>4284</v>
+      <c r="D876" s="3">
+        <v>7</v>
       </c>
       <c r="E876" s="3" t="s">
         <v>33</v>
@@ -60597,8 +60582,8 @@
       <c r="C877" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D877" s="3" t="s">
-        <v>4284</v>
+      <c r="D877" s="3">
+        <v>7</v>
       </c>
       <c r="E877" s="3" t="s">
         <v>33</v>
@@ -60651,8 +60636,8 @@
       <c r="C878" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D878" s="3" t="s">
-        <v>4284</v>
+      <c r="D878" s="3">
+        <v>7</v>
       </c>
       <c r="E878" s="3" t="s">
         <v>33</v>
@@ -60699,8 +60684,8 @@
       <c r="C879" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D879" s="3" t="s">
-        <v>4284</v>
+      <c r="D879" s="3">
+        <v>7</v>
       </c>
       <c r="E879" s="3" t="s">
         <v>33</v>
@@ -60749,8 +60734,8 @@
       <c r="C880" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D880" s="3" t="s">
-        <v>4284</v>
+      <c r="D880" s="3">
+        <v>7</v>
       </c>
       <c r="E880" s="3" t="s">
         <v>33</v>
@@ -60799,8 +60784,8 @@
       <c r="C881" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D881" s="3" t="s">
-        <v>4284</v>
+      <c r="D881" s="3">
+        <v>7</v>
       </c>
       <c r="E881" s="3" t="s">
         <v>33</v>
@@ -60849,8 +60834,8 @@
       <c r="C882" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D882" s="3" t="s">
-        <v>4284</v>
+      <c r="D882" s="3">
+        <v>7</v>
       </c>
       <c r="E882" s="3" t="s">
         <v>33</v>
@@ -60899,8 +60884,8 @@
       <c r="C883" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D883" s="3" t="s">
-        <v>4284</v>
+      <c r="D883" s="3">
+        <v>7</v>
       </c>
       <c r="E883" s="3" t="s">
         <v>33</v>
@@ -60951,8 +60936,8 @@
       <c r="C884" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D884" s="3" t="s">
-        <v>4284</v>
+      <c r="D884" s="3">
+        <v>7</v>
       </c>
       <c r="E884" s="3" t="s">
         <v>33</v>
@@ -61001,8 +60986,8 @@
       <c r="C885" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D885" s="3" t="s">
-        <v>4284</v>
+      <c r="D885" s="3">
+        <v>7</v>
       </c>
       <c r="E885" s="3" t="s">
         <v>33</v>
@@ -61185,8 +61170,8 @@
       <c r="C889" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D889" s="3" t="s">
-        <v>4284</v>
+      <c r="D889" s="3">
+        <v>7</v>
       </c>
       <c r="E889" s="3" t="s">
         <v>33</v>
@@ -61233,8 +61218,8 @@
       <c r="C890" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D890" s="3" t="s">
-        <v>4284</v>
+      <c r="D890" s="3">
+        <v>7</v>
       </c>
       <c r="E890" s="3" t="s">
         <v>33</v>
@@ -61283,8 +61268,8 @@
       <c r="C891" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D891" s="3" t="s">
-        <v>4284</v>
+      <c r="D891" s="3">
+        <v>7</v>
       </c>
       <c r="E891" s="3" t="s">
         <v>33</v>
@@ -61335,8 +61320,8 @@
       <c r="C892" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D892" s="3" t="s">
-        <v>4284</v>
+      <c r="D892" s="3">
+        <v>7</v>
       </c>
       <c r="E892" s="3" t="s">
         <v>33</v>
@@ -61671,8 +61656,8 @@
       <c r="C899" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D899" s="3" t="s">
-        <v>4284</v>
+      <c r="D899" s="3">
+        <v>7</v>
       </c>
       <c r="E899" s="3" t="s">
         <v>302</v>
@@ -61719,8 +61704,8 @@
       <c r="C900" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D900" s="3" t="s">
-        <v>4284</v>
+      <c r="D900" s="3">
+        <v>7</v>
       </c>
       <c r="E900" s="3" t="s">
         <v>302</v>
@@ -61765,8 +61750,8 @@
       <c r="C901" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D901" s="3" t="s">
-        <v>4284</v>
+      <c r="D901" s="3">
+        <v>7</v>
       </c>
       <c r="E901" s="3" t="s">
         <v>302</v>
@@ -61811,8 +61796,8 @@
       <c r="C902" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D902" s="3" t="s">
-        <v>4284</v>
+      <c r="D902" s="3">
+        <v>7</v>
       </c>
       <c r="E902" s="3" t="s">
         <v>302</v>
@@ -61857,8 +61842,8 @@
       <c r="C903" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D903" s="3" t="s">
-        <v>4284</v>
+      <c r="D903" s="3">
+        <v>7</v>
       </c>
       <c r="E903" s="3" t="s">
         <v>302</v>
@@ -61907,8 +61892,8 @@
       <c r="C904" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D904" s="3" t="s">
-        <v>4284</v>
+      <c r="D904" s="3">
+        <v>7</v>
       </c>
       <c r="E904" s="3" t="s">
         <v>302</v>
@@ -61953,8 +61938,8 @@
       <c r="C905" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D905" s="3" t="s">
-        <v>4284</v>
+      <c r="D905" s="3">
+        <v>7</v>
       </c>
       <c r="E905" s="3" t="s">
         <v>302</v>
@@ -62003,8 +61988,8 @@
       <c r="C906" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D906" s="3" t="s">
-        <v>4284</v>
+      <c r="D906" s="3">
+        <v>7</v>
       </c>
       <c r="E906" s="3" t="s">
         <v>302</v>
@@ -62053,8 +62038,8 @@
       <c r="C907" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D907" s="3" t="s">
-        <v>4284</v>
+      <c r="D907" s="3">
+        <v>7</v>
       </c>
       <c r="E907" s="3" t="s">
         <v>302</v>
@@ -62100,7 +62085,7 @@
         <v>4274</v>
       </c>
       <c r="D908" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E908" s="3" t="s">
         <v>215</v>
@@ -62149,8 +62134,8 @@
       <c r="C909" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D909" s="3" t="s">
-        <v>4284</v>
+      <c r="D909" s="3">
+        <v>7</v>
       </c>
       <c r="E909" s="3" t="s">
         <v>302</v>
@@ -62197,8 +62182,8 @@
         <v>2922</v>
       </c>
       <c r="C910" s="2"/>
-      <c r="D910" s="2" t="s">
-        <v>4284</v>
+      <c r="D910" s="2">
+        <v>7</v>
       </c>
       <c r="E910" s="3" t="s">
         <v>33</v>
@@ -62861,8 +62846,8 @@
       <c r="C925" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D925" s="3" t="s">
-        <v>4289</v>
+      <c r="D925" s="3">
+        <v>9</v>
       </c>
       <c r="E925" s="3" t="s">
         <v>86</v>
@@ -63924,7 +63909,7 @@
         <v>4273</v>
       </c>
       <c r="D950" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E950" s="3" t="s">
         <v>498</v>
@@ -63978,7 +63963,7 @@
         <v>4274</v>
       </c>
       <c r="D951" s="3" t="s">
-        <v>4318</v>
+        <v>4312</v>
       </c>
       <c r="E951" s="3" t="s">
         <v>1566</v>
@@ -64032,7 +64017,7 @@
         <v>4273</v>
       </c>
       <c r="D952" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E952" s="3" t="s">
         <v>215</v>
@@ -64135,8 +64120,8 @@
       <c r="C954" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D954" s="3" t="s">
-        <v>4285</v>
+      <c r="D954" s="3">
+        <v>4</v>
       </c>
       <c r="E954" s="3" t="s">
         <v>40</v>
@@ -64189,8 +64174,8 @@
       <c r="C955" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D955" s="3" t="s">
-        <v>4285</v>
+      <c r="D955" s="3">
+        <v>4</v>
       </c>
       <c r="E955" s="3" t="s">
         <v>40</v>
@@ -64244,7 +64229,7 @@
         <v>4274</v>
       </c>
       <c r="D956" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E956" s="3" t="s">
         <v>326</v>
@@ -64297,8 +64282,8 @@
       <c r="C957" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D957" s="3" t="s">
-        <v>4284</v>
+      <c r="D957" s="3">
+        <v>7</v>
       </c>
       <c r="E957" s="3" t="s">
         <v>302</v>
@@ -64345,8 +64330,8 @@
       <c r="C958" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D958" s="3" t="s">
-        <v>4289</v>
+      <c r="D958" s="3">
+        <v>9</v>
       </c>
       <c r="E958" s="3" t="s">
         <v>86</v>
@@ -64400,7 +64385,7 @@
         <v>4273</v>
       </c>
       <c r="D959" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E959" s="3" t="s">
         <v>293</v>
@@ -64454,7 +64439,7 @@
         <v>4273</v>
       </c>
       <c r="D960" s="3" t="s">
-        <v>4314</v>
+        <v>4308</v>
       </c>
       <c r="E960" s="3" t="s">
         <v>1037</v>
@@ -64507,8 +64492,8 @@
       <c r="C961" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D961" s="3" t="s">
-        <v>4293</v>
+      <c r="D961" s="3">
+        <v>6</v>
       </c>
       <c r="E961" s="3" t="s">
         <v>122</v>
@@ -64561,8 +64546,8 @@
       <c r="C962" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D962" s="3" t="s">
-        <v>4286</v>
+      <c r="D962" s="3">
+        <v>8</v>
       </c>
       <c r="E962" s="3" t="s">
         <v>57</v>
@@ -64615,8 +64600,8 @@
       <c r="C963" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D963" s="3" t="s">
-        <v>4284</v>
+      <c r="D963" s="3">
+        <v>7</v>
       </c>
       <c r="E963" s="3" t="s">
         <v>33</v>
@@ -64670,7 +64655,7 @@
         <v>4274</v>
       </c>
       <c r="D964" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E964" s="3" t="s">
         <v>215</v>
@@ -64777,8 +64762,8 @@
       <c r="C966" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D966" s="3" t="s">
-        <v>4286</v>
+      <c r="D966" s="3">
+        <v>8</v>
       </c>
       <c r="E966" s="3" t="s">
         <v>57</v>
@@ -64831,8 +64816,8 @@
       <c r="C967" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D967" s="3" t="s">
-        <v>4293</v>
+      <c r="D967" s="3">
+        <v>6</v>
       </c>
       <c r="E967" s="3" t="s">
         <v>122</v>
@@ -64886,7 +64871,7 @@
         <v>4273</v>
       </c>
       <c r="D968" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E968" s="3" t="s">
         <v>566</v>
@@ -65037,8 +65022,8 @@
       <c r="C971" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D971" s="3" t="s">
-        <v>4293</v>
+      <c r="D971" s="3">
+        <v>6</v>
       </c>
       <c r="E971" s="3" t="s">
         <v>122</v>
@@ -65092,7 +65077,7 @@
         <v>4276</v>
       </c>
       <c r="D972" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E972" s="3" t="s">
         <v>177</v>
@@ -65142,7 +65127,7 @@
         <v>4274</v>
       </c>
       <c r="D973" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E973" s="3" t="s">
         <v>215</v>
@@ -65196,7 +65181,7 @@
         <v>4273</v>
       </c>
       <c r="D974" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E974" s="3" t="s">
         <v>222</v>
@@ -65249,8 +65234,8 @@
       <c r="C975" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D975" s="3" t="s">
-        <v>4289</v>
+      <c r="D975" s="3">
+        <v>9</v>
       </c>
       <c r="E975" s="3" t="s">
         <v>86</v>
@@ -65300,7 +65285,7 @@
         <v>4274</v>
       </c>
       <c r="D976" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E976" s="3" t="s">
         <v>96</v>
@@ -65354,7 +65339,7 @@
         <v>4273</v>
       </c>
       <c r="D977" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E977" s="3" t="s">
         <v>215</v>
@@ -65407,8 +65392,8 @@
       <c r="C978" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D978" s="3" t="s">
-        <v>4287</v>
+      <c r="D978" s="3">
+        <v>5</v>
       </c>
       <c r="E978" s="3" t="s">
         <v>64</v>
@@ -65550,7 +65535,7 @@
         <v>4275</v>
       </c>
       <c r="D981" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E981" s="3" t="s">
         <v>326</v>
@@ -65950,7 +65935,7 @@
         <v>4274</v>
       </c>
       <c r="D989" s="3" t="s">
-        <v>4323</v>
+        <v>4317</v>
       </c>
       <c r="E989" s="3" t="s">
         <v>2617</v>
@@ -66004,7 +65989,7 @@
         <v>4273</v>
       </c>
       <c r="D990" s="3" t="s">
-        <v>4323</v>
+        <v>4317</v>
       </c>
       <c r="E990" s="3" t="s">
         <v>2617</v>
@@ -66154,7 +66139,7 @@
         <v>4275</v>
       </c>
       <c r="D993" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E993" s="3" t="s">
         <v>215</v>
@@ -66207,8 +66192,8 @@
       <c r="C994" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D994" s="3" t="s">
-        <v>4284</v>
+      <c r="D994" s="3">
+        <v>7</v>
       </c>
       <c r="E994" s="3" t="s">
         <v>33</v>
@@ -66316,7 +66301,7 @@
         <v>4273</v>
       </c>
       <c r="D996" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E996" s="3" t="s">
         <v>227</v>
@@ -66413,8 +66398,8 @@
       <c r="C998" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D998" s="3" t="s">
-        <v>4286</v>
+      <c r="D998" s="3">
+        <v>8</v>
       </c>
       <c r="E998" s="3" t="s">
         <v>57</v>
@@ -66468,7 +66453,7 @@
         <v>4274</v>
       </c>
       <c r="D999" s="3" t="s">
-        <v>4325</v>
+        <v>4319</v>
       </c>
       <c r="E999" s="3" t="s">
         <v>3164</v>
@@ -66522,7 +66507,7 @@
         <v>4274</v>
       </c>
       <c r="D1000" s="3" t="s">
-        <v>4316</v>
+        <v>4310</v>
       </c>
       <c r="E1000" s="3" t="s">
         <v>1348</v>
@@ -66726,7 +66711,7 @@
         <v>4273</v>
       </c>
       <c r="D1004" s="3" t="s">
-        <v>4311</v>
+        <v>4305</v>
       </c>
       <c r="E1004" s="3" t="s">
         <v>689</v>
@@ -66779,8 +66764,8 @@
       <c r="C1005" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1005" s="3" t="s">
-        <v>4287</v>
+      <c r="D1005" s="3">
+        <v>5</v>
       </c>
       <c r="E1005" s="3" t="s">
         <v>64</v>
@@ -66834,7 +66819,7 @@
         <v>4274</v>
       </c>
       <c r="D1006" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1006" s="3" t="s">
         <v>498</v>
@@ -66888,7 +66873,7 @@
         <v>4273</v>
       </c>
       <c r="D1007" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E1007" s="3" t="s">
         <v>293</v>
@@ -66941,8 +66926,8 @@
       <c r="C1008" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1008" s="3" t="s">
-        <v>4286</v>
+      <c r="D1008" s="3">
+        <v>8</v>
       </c>
       <c r="E1008" s="3" t="s">
         <v>57</v>
@@ -66995,8 +66980,8 @@
       <c r="C1009" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1009" s="3" t="s">
-        <v>4285</v>
+      <c r="D1009" s="3">
+        <v>4</v>
       </c>
       <c r="E1009" s="3" t="s">
         <v>40</v>
@@ -67050,7 +67035,7 @@
         <v>4274</v>
       </c>
       <c r="D1010" s="3" t="s">
-        <v>4311</v>
+        <v>4305</v>
       </c>
       <c r="E1010" s="3" t="s">
         <v>689</v>
@@ -67104,7 +67089,7 @@
         <v>4273</v>
       </c>
       <c r="D1011" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E1011" s="3" t="s">
         <v>252</v>
@@ -67158,7 +67143,7 @@
         <v>4274</v>
       </c>
       <c r="D1012" s="3" t="s">
-        <v>4320</v>
+        <v>4314</v>
       </c>
       <c r="E1012" s="3" t="s">
         <v>1739</v>
@@ -67212,7 +67197,7 @@
         <v>4274</v>
       </c>
       <c r="D1013" s="3" t="s">
-        <v>4311</v>
+        <v>4305</v>
       </c>
       <c r="E1013" s="3" t="s">
         <v>689</v>
@@ -67266,7 +67251,7 @@
         <v>4273</v>
       </c>
       <c r="D1014" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E1014" s="3" t="s">
         <v>263</v>
@@ -67319,8 +67304,8 @@
       <c r="C1015" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1015" s="3" t="s">
-        <v>4287</v>
+      <c r="D1015" s="3">
+        <v>5</v>
       </c>
       <c r="E1015" s="3" t="s">
         <v>64</v>
@@ -67372,7 +67357,7 @@
         <v>4274</v>
       </c>
       <c r="D1016" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1016" s="3" t="s">
         <v>498</v>
@@ -67474,7 +67459,7 @@
         <v>4275</v>
       </c>
       <c r="D1018" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E1018" s="3" t="s">
         <v>566</v>
@@ -67528,7 +67513,7 @@
         <v>4275</v>
       </c>
       <c r="D1019" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E1019" s="3" t="s">
         <v>326</v>
@@ -67580,7 +67565,7 @@
         <v>4274</v>
       </c>
       <c r="D1020" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E1020" s="3" t="s">
         <v>263</v>
@@ -67634,7 +67619,7 @@
         <v>4274</v>
       </c>
       <c r="D1021" s="3" t="s">
-        <v>4317</v>
+        <v>4311</v>
       </c>
       <c r="E1021" s="3" t="s">
         <v>1352</v>
@@ -67684,7 +67669,7 @@
         <v>4274</v>
       </c>
       <c r="D1022" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E1022" s="3" t="s">
         <v>222</v>
@@ -67738,7 +67723,7 @@
         <v>4275</v>
       </c>
       <c r="D1023" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E1023" s="3" t="s">
         <v>263</v>
@@ -67791,8 +67776,8 @@
       <c r="C1024" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1024" s="3" t="s">
-        <v>4287</v>
+      <c r="D1024" s="3">
+        <v>5</v>
       </c>
       <c r="E1024" s="3" t="s">
         <v>64</v>
@@ -67846,7 +67831,7 @@
         <v>4276</v>
       </c>
       <c r="D1025" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E1025" s="3" t="s">
         <v>96</v>
@@ -67899,8 +67884,8 @@
       <c r="C1026" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1026" s="3" t="s">
-        <v>4293</v>
+      <c r="D1026" s="3">
+        <v>6</v>
       </c>
       <c r="E1026" s="3" t="s">
         <v>122</v>
@@ -67954,7 +67939,7 @@
         <v>4274</v>
       </c>
       <c r="D1027" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1027" s="3" t="s">
         <v>498</v>
@@ -68008,7 +67993,7 @@
         <v>4273</v>
       </c>
       <c r="D1028" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E1028" s="3" t="s">
         <v>227</v>
@@ -68058,7 +68043,7 @@
         <v>4275</v>
       </c>
       <c r="D1029" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E1029" s="3" t="s">
         <v>263</v>
@@ -68112,7 +68097,7 @@
         <v>4274</v>
       </c>
       <c r="D1030" s="3" t="s">
-        <v>4315</v>
+        <v>4309</v>
       </c>
       <c r="E1030" s="3" t="s">
         <v>1225</v>
@@ -68166,7 +68151,7 @@
         <v>4275</v>
       </c>
       <c r="D1031" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1031" s="3" t="s">
         <v>498</v>
@@ -68219,8 +68204,8 @@
       <c r="C1032" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1032" s="3" t="s">
-        <v>4284</v>
+      <c r="D1032" s="3">
+        <v>7</v>
       </c>
       <c r="E1032" s="3" t="s">
         <v>302</v>
@@ -68274,7 +68259,7 @@
         <v>4274</v>
       </c>
       <c r="D1033" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E1033" s="3" t="s">
         <v>215</v>
@@ -68328,7 +68313,7 @@
         <v>4274</v>
       </c>
       <c r="D1034" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E1034" s="3" t="s">
         <v>326</v>
@@ -68382,7 +68367,7 @@
         <v>4275</v>
       </c>
       <c r="D1035" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E1035" s="3" t="s">
         <v>263</v>
@@ -68434,7 +68419,7 @@
         <v>4274</v>
       </c>
       <c r="D1036" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E1036" s="3" t="s">
         <v>263</v>
@@ -68488,7 +68473,7 @@
         <v>4273</v>
       </c>
       <c r="D1037" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E1037" s="3" t="s">
         <v>215</v>
@@ -68590,7 +68575,7 @@
         <v>4273</v>
       </c>
       <c r="D1039" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E1039" s="3" t="s">
         <v>215</v>
@@ -68643,8 +68628,8 @@
       <c r="C1040" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1040" s="3" t="s">
-        <v>4285</v>
+      <c r="D1040" s="3">
+        <v>4</v>
       </c>
       <c r="E1040" s="3" t="s">
         <v>40</v>
@@ -68697,8 +68682,8 @@
       <c r="C1041" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D1041" s="3" t="s">
-        <v>4289</v>
+      <c r="D1041" s="3">
+        <v>9</v>
       </c>
       <c r="E1041" s="3" t="s">
         <v>86</v>
@@ -68752,7 +68737,7 @@
         <v>4273</v>
       </c>
       <c r="D1042" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E1042" s="3" t="s">
         <v>215</v>
@@ -68804,7 +68789,7 @@
         <v>4274</v>
       </c>
       <c r="D1043" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E1043" s="3" t="s">
         <v>118</v>
@@ -68857,8 +68842,8 @@
       <c r="C1044" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1044" s="3" t="s">
-        <v>4287</v>
+      <c r="D1044" s="3">
+        <v>5</v>
       </c>
       <c r="E1044" s="3" t="s">
         <v>64</v>
@@ -68966,7 +68951,7 @@
         <v>4274</v>
       </c>
       <c r="D1046" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E1046" s="3" t="s">
         <v>566</v>
@@ -69020,7 +69005,7 @@
         <v>4274</v>
       </c>
       <c r="D1047" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E1047" s="3" t="s">
         <v>252</v>
@@ -69073,8 +69058,8 @@
       <c r="C1048" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1048" s="3" t="s">
-        <v>4293</v>
+      <c r="D1048" s="3">
+        <v>6</v>
       </c>
       <c r="E1048" s="3" t="s">
         <v>122</v>
@@ -69127,8 +69112,8 @@
       <c r="C1049" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1049" s="3" t="s">
-        <v>4293</v>
+      <c r="D1049" s="3">
+        <v>6</v>
       </c>
       <c r="E1049" s="3" t="s">
         <v>122</v>
@@ -69179,8 +69164,8 @@
       <c r="C1050" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1050" s="3" t="s">
-        <v>4287</v>
+      <c r="D1050" s="3">
+        <v>5</v>
       </c>
       <c r="E1050" s="3" t="s">
         <v>64</v>
@@ -69231,8 +69216,8 @@
       <c r="C1051" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1051" s="3" t="s">
-        <v>4287</v>
+      <c r="D1051" s="3">
+        <v>5</v>
       </c>
       <c r="E1051" s="3" t="s">
         <v>64</v>
@@ -69285,8 +69270,8 @@
       <c r="C1052" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1052" s="3" t="s">
-        <v>4286</v>
+      <c r="D1052" s="3">
+        <v>8</v>
       </c>
       <c r="E1052" s="3" t="s">
         <v>57</v>
@@ -69340,7 +69325,7 @@
         <v>4275</v>
       </c>
       <c r="D1053" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E1053" s="3" t="s">
         <v>263</v>
@@ -69394,7 +69379,7 @@
         <v>4274</v>
       </c>
       <c r="D1054" s="3" t="s">
-        <v>4319</v>
+        <v>4313</v>
       </c>
       <c r="E1054" s="3" t="s">
         <v>1643</v>
@@ -69447,8 +69432,8 @@
       <c r="C1055" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1055" s="3" t="s">
-        <v>4293</v>
+      <c r="D1055" s="3">
+        <v>6</v>
       </c>
       <c r="E1055" s="3" t="s">
         <v>122</v>
@@ -69502,7 +69487,7 @@
         <v>4274</v>
       </c>
       <c r="D1056" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E1056" s="3" t="s">
         <v>215</v>
@@ -69663,8 +69648,8 @@
       <c r="C1059" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1059" s="3" t="s">
-        <v>4284</v>
+      <c r="D1059" s="3">
+        <v>7</v>
       </c>
       <c r="E1059" s="3" t="s">
         <v>33</v>
@@ -69718,7 +69703,7 @@
         <v>4274</v>
       </c>
       <c r="D1060" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E1060" s="3" t="s">
         <v>242</v>
@@ -69771,8 +69756,8 @@
       <c r="C1061" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1061" s="3" t="s">
-        <v>4284</v>
+      <c r="D1061" s="3">
+        <v>7</v>
       </c>
       <c r="E1061" s="3" t="s">
         <v>33</v>
@@ -69824,7 +69809,7 @@
         <v>4273</v>
       </c>
       <c r="D1062" s="3" t="s">
-        <v>4296</v>
+        <v>4290</v>
       </c>
       <c r="E1062" s="3" t="s">
         <v>188</v>
@@ -69926,7 +69911,7 @@
         <v>4274</v>
       </c>
       <c r="D1064" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E1064" s="3" t="s">
         <v>118</v>
@@ -69979,8 +69964,8 @@
       <c r="C1065" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1065" s="3" t="s">
-        <v>4287</v>
+      <c r="D1065" s="3">
+        <v>5</v>
       </c>
       <c r="E1065" s="3" t="s">
         <v>64</v>
@@ -70034,7 +70019,7 @@
         <v>4274</v>
       </c>
       <c r="D1066" s="3" t="s">
-        <v>4314</v>
+        <v>4308</v>
       </c>
       <c r="E1066" s="3" t="s">
         <v>1037</v>
@@ -70087,8 +70072,8 @@
       <c r="C1067" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1067" s="3" t="s">
-        <v>4293</v>
+      <c r="D1067" s="3">
+        <v>6</v>
       </c>
       <c r="E1067" s="3" t="s">
         <v>122</v>
@@ -70142,7 +70127,7 @@
         <v>4274</v>
       </c>
       <c r="D1068" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1068" s="3" t="s">
         <v>498</v>
@@ -70195,8 +70180,8 @@
       <c r="C1069" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1069" s="3" t="s">
-        <v>4284</v>
+      <c r="D1069" s="3">
+        <v>7</v>
       </c>
       <c r="E1069" s="3" t="s">
         <v>302</v>
@@ -70245,8 +70230,8 @@
       <c r="C1070" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1070" s="3" t="s">
-        <v>4286</v>
+      <c r="D1070" s="3">
+        <v>8</v>
       </c>
       <c r="E1070" s="3" t="s">
         <v>57</v>
@@ -70300,7 +70285,7 @@
         <v>4273</v>
       </c>
       <c r="D1071" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E1071" s="3" t="s">
         <v>177</v>
@@ -70353,8 +70338,8 @@
       <c r="C1072" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1072" s="3" t="s">
-        <v>4284</v>
+      <c r="D1072" s="3">
+        <v>7</v>
       </c>
       <c r="E1072" s="3" t="s">
         <v>33</v>
@@ -70407,8 +70392,8 @@
       <c r="C1073" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1073" s="3" t="s">
-        <v>4287</v>
+      <c r="D1073" s="3">
+        <v>5</v>
       </c>
       <c r="E1073" s="3" t="s">
         <v>64</v>
@@ -70461,8 +70446,8 @@
       <c r="C1074" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1074" s="3" t="s">
-        <v>4284</v>
+      <c r="D1074" s="3">
+        <v>7</v>
       </c>
       <c r="E1074" s="3" t="s">
         <v>33</v>
@@ -70516,7 +70501,7 @@
         <v>4273</v>
       </c>
       <c r="D1075" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E1075" s="3" t="s">
         <v>96</v>
@@ -70569,8 +70554,8 @@
       <c r="C1076" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1076" s="3" t="s">
-        <v>4284</v>
+      <c r="D1076" s="3">
+        <v>7</v>
       </c>
       <c r="E1076" s="3" t="s">
         <v>33</v>
@@ -70623,8 +70608,8 @@
       <c r="C1077" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1077" s="3" t="s">
-        <v>4284</v>
+      <c r="D1077" s="3">
+        <v>7</v>
       </c>
       <c r="E1077" s="3" t="s">
         <v>33</v>
@@ -70678,7 +70663,7 @@
         <v>4273</v>
       </c>
       <c r="D1078" s="3" t="s">
-        <v>4311</v>
+        <v>4305</v>
       </c>
       <c r="E1078" s="3" t="s">
         <v>689</v>
@@ -70731,8 +70716,8 @@
       <c r="C1079" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1079" s="3" t="s">
-        <v>4284</v>
+      <c r="D1079" s="3">
+        <v>7</v>
       </c>
       <c r="E1079" s="3" t="s">
         <v>33</v>
@@ -70785,8 +70770,8 @@
       <c r="C1080" s="3" t="s">
         <v>4276</v>
       </c>
-      <c r="D1080" s="3" t="s">
-        <v>4286</v>
+      <c r="D1080" s="3">
+        <v>8</v>
       </c>
       <c r="E1080" s="3" t="s">
         <v>57</v>
@@ -70840,7 +70825,7 @@
         <v>4275</v>
       </c>
       <c r="D1081" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1081" s="3" t="s">
         <v>498</v>
@@ -70893,8 +70878,8 @@
       <c r="C1082" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1082" s="3" t="s">
-        <v>4287</v>
+      <c r="D1082" s="3">
+        <v>5</v>
       </c>
       <c r="E1082" s="3" t="s">
         <v>64</v>
@@ -70946,7 +70931,7 @@
         <v>4274</v>
       </c>
       <c r="D1083" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E1083" s="3" t="s">
         <v>222</v>
@@ -71000,7 +70985,7 @@
         <v>4274</v>
       </c>
       <c r="D1084" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E1084" s="3" t="s">
         <v>118</v>
@@ -71054,7 +71039,7 @@
         <v>4274</v>
       </c>
       <c r="D1085" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E1085" s="3" t="s">
         <v>326</v>
@@ -71108,7 +71093,7 @@
         <v>4274</v>
       </c>
       <c r="D1086" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E1086" s="3" t="s">
         <v>96</v>
@@ -71162,7 +71147,7 @@
         <v>4274</v>
       </c>
       <c r="D1087" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E1087" s="3" t="s">
         <v>130</v>
@@ -71215,8 +71200,8 @@
       <c r="C1088" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1088" s="3" t="s">
-        <v>4293</v>
+      <c r="D1088" s="3">
+        <v>6</v>
       </c>
       <c r="E1088" s="3" t="s">
         <v>122</v>
@@ -71269,8 +71254,8 @@
       <c r="C1089" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1089" s="3" t="s">
-        <v>4286</v>
+      <c r="D1089" s="3">
+        <v>8</v>
       </c>
       <c r="E1089" s="3" t="s">
         <v>57</v>
@@ -71371,8 +71356,8 @@
       <c r="C1091" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1091" s="3" t="s">
-        <v>4285</v>
+      <c r="D1091" s="3">
+        <v>4</v>
       </c>
       <c r="E1091" s="3" t="s">
         <v>40</v>
@@ -71420,7 +71405,7 @@
         <v>4275</v>
       </c>
       <c r="D1092" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E1092" s="3" t="s">
         <v>96</v>
@@ -71473,8 +71458,8 @@
       <c r="C1093" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1093" s="3" t="s">
-        <v>4284</v>
+      <c r="D1093" s="3">
+        <v>7</v>
       </c>
       <c r="E1093" s="3" t="s">
         <v>33</v>
@@ -72439,8 +72424,8 @@
       <c r="C1113" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1113" s="3" t="s">
-        <v>4287</v>
+      <c r="D1113" s="3">
+        <v>5</v>
       </c>
       <c r="E1113" s="3" t="s">
         <v>64</v>
@@ -72490,7 +72475,7 @@
         <v>4275</v>
       </c>
       <c r="D1114" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E1114" s="3" t="s">
         <v>96</v>
@@ -72544,7 +72529,7 @@
         <v>4274</v>
       </c>
       <c r="D1115" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E1115" s="3" t="s">
         <v>215</v>
@@ -72597,8 +72582,8 @@
       <c r="C1116" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1116" s="3" t="s">
-        <v>4293</v>
+      <c r="D1116" s="3">
+        <v>6</v>
       </c>
       <c r="E1116" s="3" t="s">
         <v>122</v>
@@ -72652,7 +72637,7 @@
         <v>4273</v>
       </c>
       <c r="D1117" s="3" t="s">
-        <v>4294</v>
+        <v>4288</v>
       </c>
       <c r="E1117" s="3" t="s">
         <v>130</v>
@@ -72706,7 +72691,7 @@
         <v>4274</v>
       </c>
       <c r="D1118" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E1118" s="3" t="s">
         <v>96</v>
@@ -72856,7 +72841,7 @@
         <v>4274</v>
       </c>
       <c r="D1121" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E1121" s="3" t="s">
         <v>326</v>
@@ -72909,8 +72894,8 @@
       <c r="C1122" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1122" s="3" t="s">
-        <v>4284</v>
+      <c r="D1122" s="3">
+        <v>7</v>
       </c>
       <c r="E1122" s="3" t="s">
         <v>302</v>
@@ -72956,7 +72941,7 @@
         <v>4274</v>
       </c>
       <c r="D1123" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E1123" s="3" t="s">
         <v>118</v>
@@ -73010,7 +72995,7 @@
         <v>4274</v>
       </c>
       <c r="D1124" s="3" t="s">
-        <v>4322</v>
+        <v>4316</v>
       </c>
       <c r="E1124" s="3" t="s">
         <v>2523</v>
@@ -73064,7 +73049,7 @@
         <v>4273</v>
       </c>
       <c r="D1125" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1125" s="3" t="s">
         <v>498</v>
@@ -73171,8 +73156,8 @@
       <c r="C1127" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1127" s="3" t="s">
-        <v>4287</v>
+      <c r="D1127" s="3">
+        <v>5</v>
       </c>
       <c r="E1127" s="3" t="s">
         <v>64</v>
@@ -73226,7 +73211,7 @@
         <v>4275</v>
       </c>
       <c r="D1128" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E1128" s="3" t="s">
         <v>326</v>
@@ -73280,7 +73265,7 @@
         <v>4275</v>
       </c>
       <c r="D1129" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E1129" s="3" t="s">
         <v>252</v>
@@ -73334,7 +73319,7 @@
         <v>4275</v>
       </c>
       <c r="D1130" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E1130" s="3" t="s">
         <v>215</v>
@@ -73439,8 +73424,8 @@
       <c r="C1132" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1132" s="3" t="s">
-        <v>4284</v>
+      <c r="D1132" s="3">
+        <v>7</v>
       </c>
       <c r="E1132" s="3" t="s">
         <v>33</v>
@@ -73493,8 +73478,8 @@
       <c r="C1133" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1133" s="3" t="s">
-        <v>4293</v>
+      <c r="D1133" s="3">
+        <v>6</v>
       </c>
       <c r="E1133" s="3" t="s">
         <v>122</v>
@@ -73548,7 +73533,7 @@
         <v>4274</v>
       </c>
       <c r="D1134" s="3" t="s">
-        <v>4299</v>
+        <v>4293</v>
       </c>
       <c r="E1134" s="3" t="s">
         <v>242</v>
@@ -73600,7 +73585,7 @@
         <v>4274</v>
       </c>
       <c r="D1135" s="3" t="s">
-        <v>4316</v>
+        <v>4310</v>
       </c>
       <c r="E1135" s="3" t="s">
         <v>1348</v>
@@ -73652,7 +73637,7 @@
         <v>4274</v>
       </c>
       <c r="D1136" s="3" t="s">
-        <v>4325</v>
+        <v>4319</v>
       </c>
       <c r="E1136" s="3" t="s">
         <v>3164</v>
@@ -73703,8 +73688,8 @@
       <c r="C1137" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1137" s="3" t="s">
-        <v>4289</v>
+      <c r="D1137" s="3">
+        <v>9</v>
       </c>
       <c r="E1137" s="3" t="s">
         <v>86</v>
@@ -73758,7 +73743,7 @@
         <v>4273</v>
       </c>
       <c r="D1138" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E1138" s="3" t="s">
         <v>494</v>
@@ -73806,7 +73791,7 @@
         <v>4273</v>
       </c>
       <c r="D1139" s="3" t="s">
-        <v>4317</v>
+        <v>4311</v>
       </c>
       <c r="E1139" s="3" t="s">
         <v>1352</v>
@@ -73913,8 +73898,8 @@
       <c r="C1141" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1141" s="3" t="s">
-        <v>4289</v>
+      <c r="D1141" s="3">
+        <v>9</v>
       </c>
       <c r="E1141" s="3" t="s">
         <v>86</v>
@@ -73967,8 +73952,8 @@
       <c r="C1142" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1142" s="3" t="s">
-        <v>4286</v>
+      <c r="D1142" s="3">
+        <v>8</v>
       </c>
       <c r="E1142" s="3" t="s">
         <v>57</v>
@@ -74021,8 +74006,8 @@
       <c r="C1143" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1143" s="3" t="s">
-        <v>4287</v>
+      <c r="D1143" s="3">
+        <v>5</v>
       </c>
       <c r="E1143" s="3" t="s">
         <v>64</v>
@@ -74076,7 +74061,7 @@
         <v>4275</v>
       </c>
       <c r="D1144" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1144" s="3" t="s">
         <v>498</v>
@@ -74129,8 +74114,8 @@
       <c r="C1145" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1145" s="3" t="s">
-        <v>4285</v>
+      <c r="D1145" s="3">
+        <v>4</v>
       </c>
       <c r="E1145" s="3" t="s">
         <v>40</v>
@@ -74184,7 +74169,7 @@
         <v>4274</v>
       </c>
       <c r="D1146" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E1146" s="3" t="s">
         <v>293</v>
@@ -74236,7 +74221,7 @@
         <v>4273</v>
       </c>
       <c r="D1147" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E1147" s="3" t="s">
         <v>494</v>
@@ -74290,7 +74275,7 @@
         <v>4273</v>
       </c>
       <c r="D1148" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1148" s="3" t="s">
         <v>498</v>
@@ -74342,7 +74327,7 @@
         <v>4273</v>
       </c>
       <c r="D1149" s="3" t="s">
-        <v>4323</v>
+        <v>4317</v>
       </c>
       <c r="E1149" s="3" t="s">
         <v>2617</v>
@@ -74395,8 +74380,8 @@
       <c r="C1150" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1150" s="3" t="s">
-        <v>4284</v>
+      <c r="D1150" s="3">
+        <v>7</v>
       </c>
       <c r="E1150" s="3" t="s">
         <v>302</v>
@@ -74447,8 +74432,8 @@
       <c r="C1151" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1151" s="3" t="s">
-        <v>4284</v>
+      <c r="D1151" s="3">
+        <v>7</v>
       </c>
       <c r="E1151" s="3" t="s">
         <v>302</v>
@@ -74499,8 +74484,8 @@
       <c r="C1152" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1152" s="3" t="s">
-        <v>4284</v>
+      <c r="D1152" s="3">
+        <v>7</v>
       </c>
       <c r="E1152" s="3" t="s">
         <v>302</v>
@@ -74551,8 +74536,8 @@
       <c r="C1153" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1153" s="3" t="s">
-        <v>4284</v>
+      <c r="D1153" s="3">
+        <v>7</v>
       </c>
       <c r="E1153" s="3" t="s">
         <v>33</v>
@@ -74603,8 +74588,8 @@
       <c r="C1154" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1154" s="3" t="s">
-        <v>4284</v>
+      <c r="D1154" s="3">
+        <v>7</v>
       </c>
       <c r="E1154" s="3" t="s">
         <v>33</v>
@@ -74655,8 +74640,8 @@
       <c r="C1155" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1155" s="3" t="s">
-        <v>4284</v>
+      <c r="D1155" s="3">
+        <v>7</v>
       </c>
       <c r="E1155" s="3" t="s">
         <v>33</v>
@@ -74707,8 +74692,8 @@
       <c r="C1156" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1156" s="3" t="s">
-        <v>4284</v>
+      <c r="D1156" s="3">
+        <v>7</v>
       </c>
       <c r="E1156" s="3" t="s">
         <v>33</v>
@@ -74759,8 +74744,8 @@
       <c r="C1157" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1157" s="3" t="s">
-        <v>4284</v>
+      <c r="D1157" s="3">
+        <v>7</v>
       </c>
       <c r="E1157" s="3" t="s">
         <v>33</v>
@@ -74811,8 +74796,8 @@
       <c r="C1158" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1158" s="3" t="s">
-        <v>4284</v>
+      <c r="D1158" s="3">
+        <v>7</v>
       </c>
       <c r="E1158" s="3" t="s">
         <v>33</v>
@@ -74863,8 +74848,8 @@
       <c r="C1159" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1159" s="3" t="s">
-        <v>4284</v>
+      <c r="D1159" s="3">
+        <v>7</v>
       </c>
       <c r="E1159" s="3" t="s">
         <v>33</v>
@@ -74915,8 +74900,8 @@
       <c r="C1160" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1160" s="3" t="s">
-        <v>4284</v>
+      <c r="D1160" s="3">
+        <v>7</v>
       </c>
       <c r="E1160" s="3" t="s">
         <v>33</v>
@@ -74967,8 +74952,8 @@
       <c r="C1161" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1161" s="3" t="s">
-        <v>4284</v>
+      <c r="D1161" s="3">
+        <v>7</v>
       </c>
       <c r="E1161" s="3" t="s">
         <v>33</v>
@@ -75019,8 +75004,8 @@
       <c r="C1162" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1162" s="3" t="s">
-        <v>4284</v>
+      <c r="D1162" s="3">
+        <v>7</v>
       </c>
       <c r="E1162" s="3" t="s">
         <v>33</v>
@@ -75073,8 +75058,8 @@
       <c r="C1163" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1163" s="3" t="s">
-        <v>4284</v>
+      <c r="D1163" s="3">
+        <v>7</v>
       </c>
       <c r="E1163" s="3" t="s">
         <v>33</v>
@@ -75127,8 +75112,8 @@
       <c r="C1164" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1164" s="3" t="s">
-        <v>4284</v>
+      <c r="D1164" s="3">
+        <v>7</v>
       </c>
       <c r="E1164" s="3" t="s">
         <v>33</v>
@@ -75181,8 +75166,8 @@
       <c r="C1165" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1165" s="3" t="s">
-        <v>4284</v>
+      <c r="D1165" s="3">
+        <v>7</v>
       </c>
       <c r="E1165" s="3" t="s">
         <v>33</v>
@@ -75231,8 +75216,8 @@
       <c r="C1166" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1166" s="3" t="s">
-        <v>4284</v>
+      <c r="D1166" s="3">
+        <v>7</v>
       </c>
       <c r="E1166" s="3" t="s">
         <v>33</v>
@@ -75330,7 +75315,7 @@
         <v>4274</v>
       </c>
       <c r="D1168" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1168" s="3" t="s">
         <v>498</v>
@@ -75377,8 +75362,8 @@
       <c r="C1169" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1169" s="3" t="s">
-        <v>4284</v>
+      <c r="D1169" s="3">
+        <v>7</v>
       </c>
       <c r="E1169" s="3" t="s">
         <v>33</v>
@@ -75427,8 +75412,8 @@
       <c r="C1170" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1170" s="3" t="s">
-        <v>4284</v>
+      <c r="D1170" s="3">
+        <v>7</v>
       </c>
       <c r="E1170" s="3" t="s">
         <v>33</v>
@@ -75526,7 +75511,7 @@
         <v>4276</v>
       </c>
       <c r="D1172" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1172" s="3" t="s">
         <v>498</v>
@@ -75741,8 +75726,8 @@
       <c r="C1176" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1176" s="3" t="s">
-        <v>4287</v>
+      <c r="D1176" s="3">
+        <v>5</v>
       </c>
       <c r="E1176" s="3" t="s">
         <v>64</v>
@@ -75796,7 +75781,7 @@
         <v>4274</v>
       </c>
       <c r="D1177" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E1177" s="3" t="s">
         <v>252</v>
@@ -75850,7 +75835,7 @@
         <v>4275</v>
       </c>
       <c r="D1178" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1178" s="3" t="s">
         <v>268</v>
@@ -75899,8 +75884,8 @@
       <c r="C1179" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1179" s="3" t="s">
-        <v>4284</v>
+      <c r="D1179" s="3">
+        <v>7</v>
       </c>
       <c r="E1179" s="3" t="s">
         <v>33</v>
@@ -75953,8 +75938,8 @@
       <c r="C1180" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1180" s="3" t="s">
-        <v>4293</v>
+      <c r="D1180" s="3">
+        <v>6</v>
       </c>
       <c r="E1180" s="3" t="s">
         <v>122</v>
@@ -76008,7 +75993,7 @@
         <v>4276</v>
       </c>
       <c r="D1181" s="3" t="s">
-        <v>4302</v>
+        <v>4296</v>
       </c>
       <c r="E1181" s="3" t="s">
         <v>498</v>
@@ -76061,8 +76046,8 @@
       <c r="C1182" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1182" s="3" t="s">
-        <v>4285</v>
+      <c r="D1182" s="3">
+        <v>4</v>
       </c>
       <c r="E1182" s="3" t="s">
         <v>40</v>
@@ -76115,8 +76100,8 @@
       <c r="C1183" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1183" s="3" t="s">
-        <v>4284</v>
+      <c r="D1183" s="3">
+        <v>7</v>
       </c>
       <c r="E1183" s="3" t="s">
         <v>302</v>
@@ -76167,8 +76152,8 @@
       <c r="C1184" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1184" s="3" t="s">
-        <v>4293</v>
+      <c r="D1184" s="3">
+        <v>6</v>
       </c>
       <c r="E1184" s="3" t="s">
         <v>896</v>
@@ -76219,8 +76204,8 @@
       <c r="C1185" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1185" s="3" t="s">
-        <v>4286</v>
+      <c r="D1185" s="3">
+        <v>8</v>
       </c>
       <c r="E1185" s="3" t="s">
         <v>57</v>
@@ -76273,8 +76258,8 @@
       <c r="C1186" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1186" s="3" t="s">
-        <v>4285</v>
+      <c r="D1186" s="3">
+        <v>4</v>
       </c>
       <c r="E1186" s="3" t="s">
         <v>40</v>
@@ -76328,7 +76313,7 @@
         <v>4274</v>
       </c>
       <c r="D1187" s="3" t="s">
-        <v>4303</v>
+        <v>4297</v>
       </c>
       <c r="E1187" s="3" t="s">
         <v>293</v>
@@ -76382,7 +76367,7 @@
         <v>4274</v>
       </c>
       <c r="D1188" s="3" t="s">
-        <v>4301</v>
+        <v>4295</v>
       </c>
       <c r="E1188" s="3" t="s">
         <v>263</v>
@@ -76435,8 +76420,8 @@
       <c r="C1189" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1189" s="3" t="s">
-        <v>4293</v>
+      <c r="D1189" s="3">
+        <v>6</v>
       </c>
       <c r="E1189" s="3" t="s">
         <v>122</v>
@@ -76543,8 +76528,8 @@
       <c r="C1191" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1191" s="3" t="s">
-        <v>4287</v>
+      <c r="D1191" s="3">
+        <v>5</v>
       </c>
       <c r="E1191" s="3" t="s">
         <v>64</v>
@@ -76598,7 +76583,7 @@
         <v>4274</v>
       </c>
       <c r="D1192" s="3" t="s">
-        <v>4290</v>
+        <v>4285</v>
       </c>
       <c r="E1192" s="3" t="s">
         <v>96</v>
@@ -76651,8 +76636,8 @@
       <c r="C1193" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1193" s="3" t="s">
-        <v>4287</v>
+      <c r="D1193" s="3">
+        <v>5</v>
       </c>
       <c r="E1193" s="3" t="s">
         <v>64</v>
@@ -76814,7 +76799,7 @@
         <v>4273</v>
       </c>
       <c r="D1196" s="3" t="s">
-        <v>4323</v>
+        <v>4317</v>
       </c>
       <c r="E1196" s="3" t="s">
         <v>3832</v>
@@ -76867,8 +76852,8 @@
       <c r="C1197" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1197" s="3" t="s">
-        <v>4293</v>
+      <c r="D1197" s="3">
+        <v>6</v>
       </c>
       <c r="E1197" s="3" t="s">
         <v>122</v>
@@ -76922,7 +76907,7 @@
         <v>4275</v>
       </c>
       <c r="D1198" s="3" t="s">
-        <v>4323</v>
+        <v>4317</v>
       </c>
       <c r="E1198" s="3" t="s">
         <v>3832</v>
@@ -77029,8 +77014,8 @@
       <c r="C1200" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1200" s="3" t="s">
-        <v>4286</v>
+      <c r="D1200" s="3">
+        <v>8</v>
       </c>
       <c r="E1200" s="3" t="s">
         <v>57</v>
@@ -77084,7 +77069,7 @@
         <v>4274</v>
       </c>
       <c r="D1201" s="3" t="s">
-        <v>4305</v>
+        <v>4299</v>
       </c>
       <c r="E1201" s="3" t="s">
         <v>333</v>
@@ -77138,7 +77123,7 @@
         <v>4273</v>
       </c>
       <c r="D1202" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E1202" s="3" t="s">
         <v>326</v>
@@ -77191,8 +77176,8 @@
       <c r="C1203" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1203" s="3" t="s">
-        <v>4285</v>
+      <c r="D1203" s="3">
+        <v>4</v>
       </c>
       <c r="E1203" s="3" t="s">
         <v>40</v>
@@ -77245,8 +77230,8 @@
       <c r="C1204" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1204" s="3" t="s">
-        <v>4293</v>
+      <c r="D1204" s="3">
+        <v>6</v>
       </c>
       <c r="E1204" s="3" t="s">
         <v>896</v>
@@ -77393,8 +77378,8 @@
       <c r="C1207" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1207" s="3" t="s">
-        <v>4293</v>
+      <c r="D1207" s="3">
+        <v>6</v>
       </c>
       <c r="E1207" s="3" t="s">
         <v>896</v>
@@ -77443,8 +77428,8 @@
       <c r="C1208" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1208" s="3" t="s">
-        <v>4293</v>
+      <c r="D1208" s="3">
+        <v>6</v>
       </c>
       <c r="E1208" s="3" t="s">
         <v>896</v>
@@ -77493,8 +77478,8 @@
       <c r="C1209" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1209" s="3" t="s">
-        <v>4284</v>
+      <c r="D1209" s="3">
+        <v>7</v>
       </c>
       <c r="E1209" s="3" t="s">
         <v>33</v>
@@ -77547,8 +77532,8 @@
       <c r="C1210" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1210" s="3" t="s">
-        <v>4284</v>
+      <c r="D1210" s="3">
+        <v>7</v>
       </c>
       <c r="E1210" s="3" t="s">
         <v>33</v>
@@ -77601,8 +77586,8 @@
       <c r="C1211" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1211" s="3" t="s">
-        <v>4284</v>
+      <c r="D1211" s="3">
+        <v>7</v>
       </c>
       <c r="E1211" s="3" t="s">
         <v>302</v>
@@ -77655,8 +77640,8 @@
       <c r="C1212" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1212" s="3" t="s">
-        <v>4284</v>
+      <c r="D1212" s="3">
+        <v>7</v>
       </c>
       <c r="E1212" s="3" t="s">
         <v>33</v>
@@ -77709,8 +77694,8 @@
       <c r="C1213" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1213" s="3" t="s">
-        <v>4284</v>
+      <c r="D1213" s="3">
+        <v>7</v>
       </c>
       <c r="E1213" s="3" t="s">
         <v>302</v>
@@ -78633,8 +78618,8 @@
       <c r="C1232" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1232" s="3" t="s">
-        <v>4293</v>
+      <c r="D1232" s="3">
+        <v>6</v>
       </c>
       <c r="E1232" s="3" t="s">
         <v>896</v>
@@ -78739,8 +78724,8 @@
       <c r="C1234" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1234" s="3" t="s">
-        <v>4293</v>
+      <c r="D1234" s="3">
+        <v>6</v>
       </c>
       <c r="E1234" s="3" t="s">
         <v>122</v>
@@ -78791,8 +78776,8 @@
       <c r="C1235" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1235" s="3" t="s">
-        <v>4293</v>
+      <c r="D1235" s="3">
+        <v>6</v>
       </c>
       <c r="E1235" s="3" t="s">
         <v>122</v>
@@ -78843,8 +78828,8 @@
       <c r="C1236" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1236" s="3" t="s">
-        <v>4293</v>
+      <c r="D1236" s="3">
+        <v>6</v>
       </c>
       <c r="E1236" s="3" t="s">
         <v>896</v>
@@ -78895,8 +78880,8 @@
       <c r="C1237" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1237" s="3" t="s">
-        <v>4293</v>
+      <c r="D1237" s="3">
+        <v>6</v>
       </c>
       <c r="E1237" s="3" t="s">
         <v>896</v>
@@ -78948,7 +78933,7 @@
         <v>4274</v>
       </c>
       <c r="D1238" s="3" t="s">
-        <v>4296</v>
+        <v>4290</v>
       </c>
       <c r="E1238" s="3" t="s">
         <v>188</v>
@@ -79001,8 +78986,8 @@
       <c r="C1239" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1239" s="3" t="s">
-        <v>4293</v>
+      <c r="D1239" s="3">
+        <v>6</v>
       </c>
       <c r="E1239" s="3" t="s">
         <v>896</v>
@@ -79051,8 +79036,8 @@
       <c r="C1240" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1240" s="3" t="s">
-        <v>4293</v>
+      <c r="D1240" s="3">
+        <v>6</v>
       </c>
       <c r="E1240" s="3" t="s">
         <v>896</v>
@@ -79101,8 +79086,8 @@
       <c r="C1241" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1241" s="3" t="s">
-        <v>4293</v>
+      <c r="D1241" s="3">
+        <v>6</v>
       </c>
       <c r="E1241" s="3" t="s">
         <v>896</v>
@@ -79151,8 +79136,8 @@
       <c r="C1242" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1242" s="3" t="s">
-        <v>4293</v>
+      <c r="D1242" s="3">
+        <v>6</v>
       </c>
       <c r="E1242" s="3" t="s">
         <v>896</v>
@@ -79201,8 +79186,8 @@
       <c r="C1243" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1243" s="3" t="s">
-        <v>4293</v>
+      <c r="D1243" s="3">
+        <v>6</v>
       </c>
       <c r="E1243" s="3" t="s">
         <v>896</v>
@@ -79251,8 +79236,8 @@
       <c r="C1244" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1244" s="3" t="s">
-        <v>4284</v>
+      <c r="D1244" s="3">
+        <v>7</v>
       </c>
       <c r="E1244" s="3" t="s">
         <v>302</v>
@@ -79303,8 +79288,8 @@
       <c r="C1245" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1245" s="3" t="s">
-        <v>4289</v>
+      <c r="D1245" s="3">
+        <v>9</v>
       </c>
       <c r="E1245" s="3" t="s">
         <v>86</v>
@@ -79357,8 +79342,8 @@
       <c r="C1246" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1246" s="3" t="s">
-        <v>4287</v>
+      <c r="D1246" s="3">
+        <v>5</v>
       </c>
       <c r="E1246" s="3" t="s">
         <v>64</v>
@@ -79412,7 +79397,7 @@
         <v>4273</v>
       </c>
       <c r="D1247" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E1247" s="3" t="s">
         <v>215</v>
@@ -79466,7 +79451,7 @@
         <v>4274</v>
       </c>
       <c r="D1248" s="3" t="s">
-        <v>4304</v>
+        <v>4298</v>
       </c>
       <c r="E1248" s="3" t="s">
         <v>326</v>
@@ -79519,8 +79504,8 @@
       <c r="C1249" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1249" s="3" t="s">
-        <v>4284</v>
+      <c r="D1249" s="3">
+        <v>7</v>
       </c>
       <c r="E1249" s="3" t="s">
         <v>302</v>
@@ -79571,8 +79556,8 @@
       <c r="C1250" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1250" s="3" t="s">
-        <v>4284</v>
+      <c r="D1250" s="3">
+        <v>7</v>
       </c>
       <c r="E1250" s="3" t="s">
         <v>302</v>
@@ -79623,8 +79608,8 @@
       <c r="C1251" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1251" s="3" t="s">
-        <v>4284</v>
+      <c r="D1251" s="3">
+        <v>7</v>
       </c>
       <c r="E1251" s="3" t="s">
         <v>302</v>
@@ -79728,7 +79713,7 @@
         <v>4274</v>
       </c>
       <c r="D1253" s="3" t="s">
-        <v>4292</v>
+        <v>4287</v>
       </c>
       <c r="E1253" s="3" t="s">
         <v>118</v>
@@ -79782,7 +79767,7 @@
         <v>4274</v>
       </c>
       <c r="D1254" s="3" t="s">
-        <v>4296</v>
+        <v>4290</v>
       </c>
       <c r="E1254" s="3" t="s">
         <v>188</v>
@@ -79835,8 +79820,8 @@
       <c r="C1255" s="3" t="s">
         <v>4271</v>
       </c>
-      <c r="D1255" s="3" t="s">
-        <v>4284</v>
+      <c r="D1255" s="3">
+        <v>7</v>
       </c>
       <c r="E1255" s="3" t="s">
         <v>33</v>
@@ -79887,8 +79872,8 @@
       <c r="C1256" s="3" t="s">
         <v>4271</v>
       </c>
-      <c r="D1256" s="3" t="s">
-        <v>4284</v>
+      <c r="D1256" s="3">
+        <v>7</v>
       </c>
       <c r="E1256" s="3" t="s">
         <v>33</v>
@@ -79939,8 +79924,8 @@
       <c r="C1257" s="3" t="s">
         <v>4271</v>
       </c>
-      <c r="D1257" s="3" t="s">
-        <v>4284</v>
+      <c r="D1257" s="3">
+        <v>7</v>
       </c>
       <c r="E1257" s="3" t="s">
         <v>33</v>
@@ -79991,8 +79976,8 @@
       <c r="C1258" s="3" t="s">
         <v>4271</v>
       </c>
-      <c r="D1258" s="3" t="s">
-        <v>4284</v>
+      <c r="D1258" s="3">
+        <v>7</v>
       </c>
       <c r="E1258" s="3" t="s">
         <v>33</v>
@@ -80043,8 +80028,8 @@
       <c r="C1259" s="3" t="s">
         <v>4271</v>
       </c>
-      <c r="D1259" s="3" t="s">
-        <v>4284</v>
+      <c r="D1259" s="3">
+        <v>7</v>
       </c>
       <c r="E1259" s="3" t="s">
         <v>33</v>
@@ -80148,7 +80133,7 @@
         <v>4274</v>
       </c>
       <c r="D1261" s="3" t="s">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="E1261" s="3" t="s">
         <v>222</v>
@@ -80202,7 +80187,7 @@
         <v>4274</v>
       </c>
       <c r="D1262" s="3" t="s">
-        <v>4298</v>
+        <v>4292</v>
       </c>
       <c r="E1262" s="3" t="s">
         <v>227</v>
@@ -80256,7 +80241,7 @@
         <v>4274</v>
       </c>
       <c r="D1263" s="3" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="E1263" s="3" t="s">
         <v>566</v>
@@ -80309,8 +80294,8 @@
       <c r="C1264" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1264" s="3" t="s">
-        <v>4287</v>
+      <c r="D1264" s="3">
+        <v>5</v>
       </c>
       <c r="E1264" s="3" t="s">
         <v>64</v>
@@ -80883,8 +80868,8 @@
       <c r="C1275" s="3" t="s">
         <v>4275</v>
       </c>
-      <c r="D1275" s="3" t="s">
-        <v>4293</v>
+      <c r="D1275" s="3">
+        <v>6</v>
       </c>
       <c r="E1275" s="3" t="s">
         <v>896</v>
@@ -81095,8 +81080,8 @@
       <c r="C1279" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1279" s="3" t="s">
-        <v>4284</v>
+      <c r="D1279" s="3">
+        <v>7</v>
       </c>
       <c r="E1279" s="3" t="s">
         <v>33</v>
@@ -81149,8 +81134,8 @@
       <c r="C1280" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1280" s="3" t="s">
-        <v>4284</v>
+      <c r="D1280" s="3">
+        <v>7</v>
       </c>
       <c r="E1280" s="3" t="s">
         <v>33</v>
@@ -81203,8 +81188,8 @@
       <c r="C1281" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1281" s="3" t="s">
-        <v>4284</v>
+      <c r="D1281" s="3">
+        <v>7</v>
       </c>
       <c r="E1281" s="3" t="s">
         <v>33</v>
@@ -81257,8 +81242,8 @@
       <c r="C1282" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1282" s="3" t="s">
-        <v>4284</v>
+      <c r="D1282" s="3">
+        <v>7</v>
       </c>
       <c r="E1282" s="3" t="s">
         <v>33</v>
@@ -81311,8 +81296,8 @@
       <c r="C1283" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1283" s="3" t="s">
-        <v>4284</v>
+      <c r="D1283" s="3">
+        <v>7</v>
       </c>
       <c r="E1283" s="3" t="s">
         <v>33</v>
@@ -81365,8 +81350,8 @@
       <c r="C1284" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1284" s="3" t="s">
-        <v>4284</v>
+      <c r="D1284" s="3">
+        <v>7</v>
       </c>
       <c r="E1284" s="3" t="s">
         <v>33</v>
@@ -81419,8 +81404,8 @@
       <c r="C1285" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1285" s="3" t="s">
-        <v>4284</v>
+      <c r="D1285" s="3">
+        <v>7</v>
       </c>
       <c r="E1285" s="3" t="s">
         <v>33</v>
@@ -81473,8 +81458,8 @@
       <c r="C1286" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1286" s="3" t="s">
-        <v>4284</v>
+      <c r="D1286" s="3">
+        <v>7</v>
       </c>
       <c r="E1286" s="3" t="s">
         <v>33</v>
@@ -81527,8 +81512,8 @@
       <c r="C1287" s="3" t="s">
         <v>4273</v>
       </c>
-      <c r="D1287" s="3" t="s">
-        <v>4284</v>
+      <c r="D1287" s="3">
+        <v>7</v>
       </c>
       <c r="E1287" s="3" t="s">
         <v>33</v>
@@ -82002,7 +81987,7 @@
         <v>4274</v>
       </c>
       <c r="D1296" s="3" t="s">
-        <v>4306</v>
+        <v>4300</v>
       </c>
       <c r="E1296" s="3" t="s">
         <v>494</v>
@@ -82050,7 +82035,7 @@
         <v>4274</v>
       </c>
       <c r="D1297" s="3" t="s">
-        <v>4300</v>
+        <v>4294</v>
       </c>
       <c r="E1297" s="3" t="s">
         <v>252</v>
@@ -82099,8 +82084,8 @@
       <c r="C1298" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1298" s="3" t="s">
-        <v>4284</v>
+      <c r="D1298" s="3">
+        <v>7</v>
       </c>
       <c r="E1298" s="3" t="s">
         <v>33</v>
@@ -82151,8 +82136,8 @@
       <c r="C1299" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1299" s="3" t="s">
-        <v>4284</v>
+      <c r="D1299" s="3">
+        <v>7</v>
       </c>
       <c r="E1299" s="3" t="s">
         <v>33</v>
@@ -82203,8 +82188,8 @@
       <c r="C1300" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1300" s="3" t="s">
-        <v>4284</v>
+      <c r="D1300" s="3">
+        <v>7</v>
       </c>
       <c r="E1300" s="3" t="s">
         <v>33</v>
@@ -82257,8 +82242,8 @@
       <c r="C1301" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1301" s="3" t="s">
-        <v>4284</v>
+      <c r="D1301" s="3">
+        <v>7</v>
       </c>
       <c r="E1301" s="3" t="s">
         <v>33</v>
@@ -82309,8 +82294,8 @@
       <c r="C1302" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1302" s="3" t="s">
-        <v>4284</v>
+      <c r="D1302" s="3">
+        <v>7</v>
       </c>
       <c r="E1302" s="3" t="s">
         <v>33</v>
@@ -82361,8 +82346,8 @@
       <c r="C1303" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1303" s="3" t="s">
-        <v>4284</v>
+      <c r="D1303" s="3">
+        <v>7</v>
       </c>
       <c r="E1303" s="3" t="s">
         <v>302</v>
@@ -82413,8 +82398,8 @@
       <c r="C1304" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1304" s="3" t="s">
-        <v>4284</v>
+      <c r="D1304" s="3">
+        <v>7</v>
       </c>
       <c r="E1304" s="3" t="s">
         <v>33</v>
@@ -82465,8 +82450,8 @@
       <c r="C1305" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1305" s="3" t="s">
-        <v>4284</v>
+      <c r="D1305" s="3">
+        <v>7</v>
       </c>
       <c r="E1305" s="3" t="s">
         <v>33</v>
@@ -82519,8 +82504,8 @@
       <c r="C1306" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1306" s="3" t="s">
-        <v>4284</v>
+      <c r="D1306" s="3">
+        <v>7</v>
       </c>
       <c r="E1306" s="3" t="s">
         <v>302</v>
@@ -82571,8 +82556,8 @@
       <c r="C1307" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1307" s="3" t="s">
-        <v>4284</v>
+      <c r="D1307" s="3">
+        <v>7</v>
       </c>
       <c r="E1307" s="3" t="s">
         <v>33</v>
@@ -82625,8 +82610,8 @@
       <c r="C1308" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1308" s="3" t="s">
-        <v>4293</v>
+      <c r="D1308" s="3">
+        <v>6</v>
       </c>
       <c r="E1308" s="3" t="s">
         <v>122</v>
@@ -82679,8 +82664,8 @@
       <c r="C1309" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1309" s="3" t="s">
-        <v>4284</v>
+      <c r="D1309" s="3">
+        <v>7</v>
       </c>
       <c r="E1309" s="3" t="s">
         <v>33</v>
@@ -82733,8 +82718,8 @@
       <c r="C1310" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1310" s="3" t="s">
-        <v>4284</v>
+      <c r="D1310" s="3">
+        <v>7</v>
       </c>
       <c r="E1310" s="3" t="s">
         <v>302</v>
@@ -82785,8 +82770,8 @@
       <c r="C1311" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1311" s="3" t="s">
-        <v>4286</v>
+      <c r="D1311" s="3">
+        <v>8</v>
       </c>
       <c r="E1311" s="3" t="s">
         <v>57</v>
@@ -82839,8 +82824,8 @@
       <c r="C1312" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1312" s="3" t="s">
-        <v>4284</v>
+      <c r="D1312" s="3">
+        <v>7</v>
       </c>
       <c r="E1312" s="3" t="s">
         <v>33</v>
@@ -82893,8 +82878,8 @@
       <c r="C1313" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1313" s="3" t="s">
-        <v>4284</v>
+      <c r="D1313" s="3">
+        <v>7</v>
       </c>
       <c r="E1313" s="3" t="s">
         <v>33</v>
@@ -82948,7 +82933,7 @@
         <v>4274</v>
       </c>
       <c r="D1314" s="3" t="s">
-        <v>4295</v>
+        <v>4289</v>
       </c>
       <c r="E1314" s="3" t="s">
         <v>215</v>
@@ -83001,8 +82986,8 @@
       <c r="C1315" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1315" s="3" t="s">
-        <v>4284</v>
+      <c r="D1315" s="3">
+        <v>7</v>
       </c>
       <c r="E1315" s="3" t="s">
         <v>33</v>
@@ -83055,8 +83040,8 @@
       <c r="C1316" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1316" s="3" t="s">
-        <v>4284</v>
+      <c r="D1316" s="3">
+        <v>7</v>
       </c>
       <c r="E1316" s="3" t="s">
         <v>302</v>
@@ -83107,8 +83092,8 @@
       <c r="C1317" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1317" s="3" t="s">
-        <v>4284</v>
+      <c r="D1317" s="3">
+        <v>7</v>
       </c>
       <c r="E1317" s="3" t="s">
         <v>33</v>
@@ -83161,8 +83146,8 @@
       <c r="C1318" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1318" s="3" t="s">
-        <v>4284</v>
+      <c r="D1318" s="3">
+        <v>7</v>
       </c>
       <c r="E1318" s="3" t="s">
         <v>302</v>
@@ -83213,8 +83198,8 @@
       <c r="C1319" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1319" s="3" t="s">
-        <v>4284</v>
+      <c r="D1319" s="3">
+        <v>7</v>
       </c>
       <c r="E1319" s="3" t="s">
         <v>33</v>
@@ -83267,8 +83252,8 @@
       <c r="C1320" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1320" s="3" t="s">
-        <v>4284</v>
+      <c r="D1320" s="3">
+        <v>7</v>
       </c>
       <c r="E1320" s="3" t="s">
         <v>302</v>
@@ -83319,8 +83304,8 @@
       <c r="C1321" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1321" s="3" t="s">
-        <v>4284</v>
+      <c r="D1321" s="3">
+        <v>7</v>
       </c>
       <c r="E1321" s="3" t="s">
         <v>33</v>
@@ -83373,8 +83358,8 @@
       <c r="C1322" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1322" s="3" t="s">
-        <v>4284</v>
+      <c r="D1322" s="3">
+        <v>7</v>
       </c>
       <c r="E1322" s="3" t="s">
         <v>302</v>
@@ -83425,8 +83410,8 @@
       <c r="C1323" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1323" s="3" t="s">
-        <v>4284</v>
+      <c r="D1323" s="3">
+        <v>7</v>
       </c>
       <c r="E1323" s="3" t="s">
         <v>302</v>
@@ -83477,8 +83462,8 @@
       <c r="C1324" s="3" t="s">
         <v>4274</v>
       </c>
-      <c r="D1324" s="3" t="s">
-        <v>4284</v>
+      <c r="D1324" s="3">
+        <v>7</v>
       </c>
       <c r="E1324" s="3" t="s">
         <v>302</v>
@@ -83521,10 +83506,11 @@
     </row>
     <row r="1325" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <autoFilter ref="D1:D1325" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="G1:J1325 F1:F1325 A1:A1325 K1:R1325 D2" numberStoredAsText="1"/>
+    <ignoredError sqref="G1:J1325 F1:F1325 A1:A1325 K1:R1325" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>